--- a/Scopezilla/DATAPREV-PAT/outputs/scoping-deliverables.xlsx
+++ b/Scopezilla/DATAPREV-PAT/outputs/scoping-deliverables.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap Phases" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles &amp; Skills" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Efficiency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercials" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimate Comparison" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimate Comparison" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +492,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Motor do 'leilão' reverso sobre SALES CLOUD com objetos NATIVOS (ADR 0004): a beneficiária cadastra a demanda como OPPORTUNITY nativa (nº funcionários, valor, vigência, distribuição por UF, recursos obrigatórios); N facilitadoras respondem com QUOTES nativas (prazo/SLA) EXCLUSIVAMENTE via API — a facilitadora NÃO tem acesso à plataforma (sem UI, sem licença de portal); submete a proposta informando o ID da cotação/oportunidade aberta dentro da vigência (G0210, confirmado grill 31/jul). COMO A FACILITADORA DESCOBRE UMA DEMANDA (decisão 31/jul): no MVP a plataforma ENTREGA UM ENDPOINT DE CONSULTA (pull via API/MuleSoft, E05) das demandas abertas na vigência — a facilitadora CONSULTA, NÃO recebe push ativo; a NOTIFICAÇÃO ATIVA (push) fica no roadmap futuro, com o CANAL A DEFINIR — a escolha do canal é o que condiciona posicionar ou não Marketing Cloud (G0209/G0211). EQUIDADE POR CONSTRUÇÃO: como a facilitadora não tem UI, ela não enxerga as propostas concorrentes — não é necessário Apex managed sharing para ocultá-las. A beneficiária VÊ as cotações conforme chegam (comparação lado a lado, LWC), mas só PODE SELECIONAR quando a janela de vigência fecha — seleção manual TRAVADA até o fechamento, não seleção cega (confirmado grill 31/jul). Camada custom fina: tela Comparar Propostas + trava de seleção até o fechamento + máquina de estados da janela → contrato firmado. CONTRATO SEM CLM no MVP (transcrição 31/jul): a facilitadora faz upload do PDF imutável do contrato + metadados + versões (aditivos/renovações como upload de nova versão); NÃO há ferramenta de contract lifecycle management nem validação automática de contrato nesta versão (roadmap futuro). PASSO NOVO — TERMO DE ACEITE (transcrição 31/jul, MVP-required): após o contrato firmado, a beneficiária dá o termo de aceite classificando nº de trabalhadores acima/abaixo de 5 salários mínimos por CNPJ e a distribuição matriz/filial — informação integrada ao Novo PAT via INIS PJ (E05). Matriz/filial: ao aderir, todas as filiais entram. BENEFICIÁRIAS PAT E NÃO-PAT (transcrição 31/jul): ambas contratam pelo marketplace, com regras de cálculo distintas (PAT sob teto 3,6%; não-PAT sem benefício fiscal → taxa diferente); contratos legados devem ser carregados. Camada custom reservada ao que o nativo não entrega (equidade, tela Comparar Propostas, seleção→contrato). Data Cloud para enriquecer histórico de facilitadoras — Assumed, candidato a de-escopo/buffer sob a janela fixa de 15/nov.</t>
+          <t>Motor do 'leilão' reverso sobre SALES CLOUD com objetos NATIVOS (ADR 0004): a beneficiária cadastra a demanda como OPPORTUNITY nativa (nº funcionários, valor, vigência, distribuição por UF, recursos obrigatórios); N facilitadoras respondem com QUOTES nativas (prazo/SLA) EXCLUSIVAMENTE via API — a facilitadora NÃO tem acesso à plataforma (sem UI, sem licença de portal); submete a proposta informando o ID da cotação/oportunidade aberta dentro da vigência (G0210, confirmado grill 31/jul). COMO A FACILITADORA DESCOBRE UMA DEMANDA (decisão 31/jul): na Fase 1 a plataforma ENTREGA UM ENDPOINT DE CONSULTA (pull via API/MuleSoft, E05) das demandas abertas na vigência — a facilitadora CONSULTA, NÃO recebe push ativo; a NOTIFICAÇÃO ATIVA (push) fica no roadmap futuro, com o CANAL A DEFINIR — a escolha do canal é o que condiciona posicionar ou não Marketing Cloud (G0209/G0211). EQUIDADE POR CONSTRUÇÃO: como a facilitadora não tem UI, ela não enxerga as propostas concorrentes — não é necessário Apex managed sharing para ocultá-las. A beneficiária VÊ as cotações conforme chegam (comparação lado a lado, LWC), mas só PODE SELECIONAR quando a janela de vigência fecha — seleção manual TRAVADA até o fechamento, não seleção cega (confirmado grill 31/jul). Camada custom fina: tela Comparar Propostas + trava de seleção até o fechamento + máquina de estados da janela → contrato firmado. CONTRATO SEM CLM na Fase 1 (transcrição 31/jul): a facilitadora faz upload do PDF imutável do contrato + metadados + versões (aditivos/renovações como upload de nova versão); NÃO há ferramenta de contract lifecycle management nem validação automática de contrato nesta versão (roadmap futuro). PASSO NOVO — TERMO DE ACEITE (transcrição 31/jul, Fase 1-required): após o contrato firmado, a beneficiária dá o termo de aceite classificando nº de trabalhadores acima/abaixo de 5 salários mínimos por CNPJ e a distribuição matriz/filial — informação integrada ao Novo PAT via INIS PJ (E05). Matriz/filial: ao aderir, todas as filiais entram. BENEFICIÁRIAS PAT E NÃO-PAT (transcrição 31/jul): ambas contratam pelo marketplace, com regras de cálculo distintas (PAT sob teto 3,6%; não-PAT sem benefício fiscal → taxa diferente); contratos legados devem ser carregados. Camada custom reservada ao que o nativo não entrega (equidade, tela Comparar Propostas, seleção→contrato). Data Cloud para enriquecer histórico de facilitadoras — Assumed, candidato a de-escopo/buffer sob a janela fixa de 15/nov.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,7 +519,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ciclo folha→pagamento→split sob a regra de repasse em até 15 dias (Decreto 12.712/2025). FLUXO (premissa 31/jul): (1) a beneficiária faz UPLOAD do CSV de folha da competência via PORTAL ou API; (2) a plataforma VALIDA o layout do arquivo e a integridade ('não quebrado') — avaliar a melhor alternativa Salesforce para as críticas (Einstein / agente / outro); (3) SEM crítica, habilita o arquivo para DOWNLOAD da facilitadora — as LINHAS DA FOLHA NÃO SÃO CARREGADAS em objeto da plataforma (necessidade futura de roadmap, não agora); (4) a facilitadora baixa a folha associada ao contrato do beneficiário na vigência mês/ano específica e DEVOLVE via API o status 'processado' + o valor a pagar; (5) a plataforma envia o valor ao GATEWAY (que intermedia a conta custódia) e recebe de volta o BOLETO REGISTRADO + metadados/link; (6) o boleto é disponibilizado à beneficiária no portal para download e pagamento; (7) a plataforma recebe do gateway as MOVIMENTAÇÕES BANCÁRIAS de forma BATCH INCREMENTAL via AGENDAMENTO no MuleSoft (E05) para identificar o pagamento e avançar status; (8) identificado o pagamento, o sistema consulta as REGRAS DE CÁLCULO DE SPLIT, calcula o repasse à facilitadora e demais empresas, e REGISTRA todo o racional (datas, split, ordens/boletagens de transferência), entregando via MuleSoft ao gateway. FRONTEIRA (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT (calcula, aplica, emite boletagem, orquestra, concilia por casamento, registra racional); o GATEWAY é o ÚNICO responsável pela EXECUÇÃO das transações bancárias e pela custódia — FORA do escopo Salesforce. UI simplificada: status consolidado 'crédito concedido' (uma linha, não lista por trabalhador); marca é o gatilho de notificação à empresa e via CTPS Digital ('expectativa de crédito', só monitoramento no MVP). Objetos custom para folha (cabeçalho/competência, sem linhas), contrato e regras de split; Revenue Cloud fora desta rodada. Lógica financeira real → XL.</t>
+          <t>Ciclo folha→pagamento→split sob a regra de repasse em até 15 dias (Decreto 12.712/2025). FLUXO (premissa 31/jul): (1) a beneficiária faz UPLOAD do CSV de folha da competência via PORTAL ou API; (2) a plataforma VALIDA o layout do arquivo e a integridade ('não quebrado') — avaliar a melhor alternativa Salesforce para as críticas (Einstein / agente / outro); (3) SEM crítica, habilita o arquivo para DOWNLOAD da facilitadora — as LINHAS DA FOLHA NÃO SÃO CARREGADAS em objeto da plataforma (necessidade futura de roadmap, não agora); (4) a facilitadora baixa a folha associada ao contrato do beneficiário na vigência mês/ano específica e DEVOLVE via API o status 'processado' + o valor a pagar; (5) a plataforma envia o valor ao GATEWAY (que intermedia a conta custódia) e recebe de volta o BOLETO REGISTRADO + metadados/link; (6) o boleto é disponibilizado à beneficiária no portal para download e pagamento; (7) a plataforma recebe do gateway as MOVIMENTAÇÕES BANCÁRIAS de forma BATCH INCREMENTAL via AGENDAMENTO no MuleSoft (E05) para identificar o pagamento e avançar status; (8) identificado o pagamento, o sistema consulta as REGRAS DE CÁLCULO DE SPLIT, calcula o repasse à facilitadora e demais empresas, e REGISTRA todo o racional (datas, split, ordens/boletagens de transferência), entregando via MuleSoft ao gateway. FRONTEIRA (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT (calcula, aplica, emite boletagem, orquestra, concilia por casamento, registra racional); o GATEWAY é o ÚNICO responsável pela EXECUÇÃO das transações bancárias e pela custódia — FORA do escopo Salesforce. UI simplificada: status consolidado 'crédito concedido' (uma linha, não lista por trabalhador); marca é o gatilho de notificação à empresa e via CTPS Digital ('expectativa de crédito', só monitoramento na Fase 1). Objetos custom para folha (cabeçalho/competência, sem linhas), contrato e regras de split; Revenue Cloud fora desta rodada. Lógica financeira real → XL.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +573,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Camada de integração API-led MuleSoft ON-PREMISE (ADR 0005 — instalado na infra Dataprev/gov, dentro do perímetro soberano; resolve G0504; ponto de de-tokenização do CPF). Conecta Novo PAT (que HOJE NÃO TEM API — transcrição 31/jul, MT/DTI: mock-first obrigatório), GOV.BR/Geride, CTPS Digital ('expectativa de crédito' ao trabalhador no processamento da folha — só monitoramento no MVP), eSocial, SDC, INIS PJ/Kinis PJ (origem do termo de aceite — nº trabalhadores por faixa salarial e matriz/filial, E02), o gateway/banco custódia (recebe a boletagem com split e o valor a pagar; devolve o boleto registrado e as MOVIMENTAÇÕES BANCÁRIAS em BATCH INCREMENTAL via AGENDAMENTO no MuleSoft — ADR 0003) e as APIs das ~600-700 facilitadoras (recepção de Quotes/propostas e devolução de processado+valor, MAIS a EXPOSIÇÃO DE UM ENDPOINT DE CONSULTA das demandas/leilões abertos na vigência — pull no MVP: a facilitadora consulta e descobre as demandas publicadas pelas beneficiárias, sem push ativo; a notificação ativa/push é roadmap futuro, com o canal a definir — E02/G0211, decisão 31/jul). ADQUIRENTE (transcrição 31/jul): API para a adquirente CONSULTAR o status de credenciamento do estabelecimento antes de processar transações; a adquirente envia TODAS as transações para monitoramento/analytics interno (antifraude/desvio) — feed de monitoramento é near-term para a consulta e V2/futuro para o analytics completo. Validação de estabelecimento por CNPJ: client credentials flow, connected app com escopo restrito, validação de token com rate limit e cache. Mock-first para desbloquear o desenvolvimento enquanto Swaggers/contratos não são disponibilizados.</t>
+          <t>Camada de integração API-led MuleSoft ON-PREMISE (ADR 0005 — instalado na infra Dataprev/gov, dentro do perímetro soberano; resolve G0504; ponto de de-tokenização do CPF). Conecta Novo PAT (que HOJE NÃO TEM API — transcrição 31/jul, MT/DTI: mock-first obrigatório), GOV.BR/Geride, CTPS Digital ('expectativa de crédito' ao trabalhador no processamento da folha — só monitoramento na Fase 1), eSocial, SDC, INIS PJ/Kinis PJ (origem do termo de aceite — nº trabalhadores por faixa salarial e matriz/filial, E02), o gateway/banco custódia (recebe a boletagem com split e o valor a pagar; devolve o boleto registrado e as MOVIMENTAÇÕES BANCÁRIAS em BATCH INCREMENTAL via AGENDAMENTO no MuleSoft — ADR 0003) e as APIs das ~600-700 facilitadoras (recepção de Quotes/propostas e devolução de processado+valor, MAIS a EXPOSIÇÃO DE UM ENDPOINT DE CONSULTA das demandas/leilões abertos na vigência — pull na Fase 1: a facilitadora consulta e descobre as demandas publicadas pelas beneficiárias, sem push ativo; a notificação ativa/push é roadmap futuro, com o canal a definir — E02/G0211, decisão 31/jul). ADQUIRENTE (transcrição 31/jul): API para a adquirente CONSULTAR o status de credenciamento do estabelecimento antes de processar transações; a adquirente envia TODAS as transações para monitoramento/analytics interno (antifraude/desvio) — feed de monitoramento é near-term para a consulta e V2/futuro para o analytics completo. Validação de estabelecimento por CNPJ: client credentials flow, connected app com escopo restrito, validação de token com rate limit e cache. Mock-first para desbloquear o desenvolvimento enquanto Swaggers/contratos não são disponibilizados.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,7 +596,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Agente informacional e transacional (WhatsApp/webchat) para atender participantes em escala (beneficiárias, facilitadoras, estabelecimentos). Canais e casos de uso (informacional vs. transacional) e integração com o marketplace a confirmar com o cliente. [FORA DO ESCOPO DO MVP — deferida para Onda 2 pós-go-live (roadmap Fase 5), retida como buffer de cronograma da janela fixa de 15/nov/2026.]</t>
+          <t>Agente informacional e transacional (WhatsApp/webchat) para atender participantes em escala (beneficiárias, facilitadoras, estabelecimentos). Canais e casos de uso (informacional vs. transacional) e integração com o marketplace a confirmar com o cliente. [FORA DO ESCOPO DO Fase 1 — deferida para Onda 2 pós-go-live (roadmap Etapa 5), retida como buffer de cronograma da janela fixa de 15/nov/2026.]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -681,6 +682,178 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration Weeks Range</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Indicative Price Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Indicative Price High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Capacity Summary</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Delta vs Other Lane</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Validated By</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Disclaimer Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>quantum-leap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'low': 11, 'high': 27}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (senior onshore); 2x Developer (regular offshore); 1x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore); 1x Developer (Scale) (regular offshore); 1x Developer (Scale) (regular offshore); 1x Technical Architect (Scale) (senior onshore); 1x Project/Program Manager (Scale) (senior onshore); 1x Product Owner / Decisor; 1x SMEs por épica; 1x Data Steward; 1x Client IT / Plataforma; 1x Capacidade de UAT; 1x Sponsor executivo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'program_avg_fte': 9.4, 'peak_distinct_people': 13, 'ps_person_hours': 5200, 'ps_person_hours_build': 4880, 'ps_person_hours_scale': 320, 'blended_rate_no_tax': 754.0, 'note': 'FTE média do build = 4.880 PS person-hours / (13 sem × 40) = 9,4. Roster re-derivado por janela no plano paralelizado: Arquiteto Técnico MuleSoft sênior ADICIONADO (frente E05 contínua S1-S11), Senior PM absorve a accountability antes do Engagement Manager (removido), devs full por todo o build (janelas longas). + 4 semanas de Scale/Hypercare (320h, reusa perfis do build; Dev MuleSoft reforçado 0,5→1,0 FTE no grill 03/ago). Pico de 13 pessoas no meio do build.'}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,91M sem imposto / R$ 4,18M com imposto (~9,4 FTE média no build). Build R$ 3,68M sem imposto; Scale R$ 0,23M sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>traditional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'low': 18, 'high': 38}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1x Project/Program Manager (senior onshore); 1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (regular onshore); 3x Developer (regular offshore); 2x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Developer (senior offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'program_avg_fte': 10.6, 'peak_distinct_people': 16, 'person_hours_range': {'low': 7420, 'high': 15670}, 'blended_rate_no_tax': 736.0, 'note': 'Pod de build offshore que escala com volume + oversight sênior onshore + especialista financeiro/bancário (E03 XL). Escopo completo (9 épicas, inclui E06).'}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,91M sem imposto / R$ 4,18M com imposto (~9,4 FTE média no build). Build R$ 3,68M sem imposto; Scale R$ 0,23M sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -693,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,7 +1173,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RESOLVIDO na direção de descoberta/notificação (decisão 31/jul): no MVP (até 15/nov) a plataforma ENTREGA UM ENDPOINT DE CONSULTA (pull via API/MuleSoft, E05) — a facilitadora CONSULTA e descobre as demandas abertas na vigência; NÃO há push ativo. Notificação ativa (push) fica no roadmap futuro, com o canal a definir (ver G0211). Coerente com facilitadora API-only (ADR 0004). PENDENTE ainda: o payload/auth/idempotência da submissão da Quote e a garantia de elegibilidade por UF (a especificar no workshop de regras do leilão, E02/Fase 2) — a mecânica de envelope fechado é resolvida por construção (facilitadora sem UI não vê concorrentes).</t>
+          <t>RESOLVIDO na direção de descoberta/notificação (decisão 31/jul): na Fase 1 (até 15/nov) a plataforma ENTREGA UM ENDPOINT DE CONSULTA (pull via API/MuleSoft, E05) — a facilitadora CONSULTA e descobre as demandas abertas na vigência; NÃO há push ativo. Notificação ativa (push) fica no roadmap futuro, com o canal a definir (ver G0211). Coerente com facilitadora API-only (ADR 0004). PENDENTE ainda: o payload/auth/idempotência da submissão da Quote e a garantia de elegibilidade por UF (a especificar no workshop de regras do leilão, E02/Etapa 2) — a mecânica de envelope fechado é resolvida por construção (facilitadora sem UI não vê concorrentes).</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1393,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Define o modelo de dados central de E04 (Estabelecimento unico vs. Credenciamento__c 1-&gt;N por facilitadora). Afeta E02 e E05. Alto impacto de sizing. Contexto de negócio (base: discovery-notes/reforma-pat-decreto-12712-2025.md): a reforma (Decreto 12.712/2025 — MDR 3,6%, repasse 15 dias, interoperabilidade) torna o cadastro unificado o value driver do estabelecimento, mas NÃO extingue o papel legal da facilitadora de aprovar/descredenciar — é essa dupla natureza (registro central único vs. relação legal por facilitadora) que gera o conflito de fonte a resolver na Fase 0. Decreto sub judice (ADI 7962/STF).</t>
+          <t>Define o modelo de dados central de E04 (Estabelecimento unico vs. Credenciamento__c 1-&gt;N por facilitadora). Afeta E02 e E05. Alto impacto de sizing. Contexto de negócio (base: discovery-notes/reforma-pat-decreto-12712-2025.md): a reforma (Decreto 12.712/2025 — MDR 3,6%, repasse 15 dias, interoperabilidade) torna o cadastro unificado o value driver do estabelecimento, mas NÃO extingue o papel legal da facilitadora de aprovar/descredenciar — é essa dupla natureza (registro central único vs. relação legal por facilitadora) que gera o conflito de fonte a resolver na Etapa 0. Decreto sub judice (ADI 7962/STF).</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1591,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fechado na direção 'on-premise'. Ainda scopezilla-recommended/Assumed no nível de premissa (a ratificar com o cliente por escrito). A infra on-premise é pré-requisito de marco da Fase 0 e carrega lead-time externo (ver risco de arranque). Não é mais bloqueador de design.</t>
+          <t>Fechado na direção 'on-premise'. Ainda scopezilla-recommended/Assumed no nível de premissa (a ratificar com o cliente por escrito). A infra on-premise é pré-requisito de marco da Etapa 0 e carrega lead-time externo (ver risco de arranque). Não é mais bloqueador de design.</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1679,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bloqueia a estimativa de E06 - T-shirt pode variar de S a XL. Recomenda-se decompor em fase informacional (MVP) + transacional (futura) ate o cliente definir casos de uso.</t>
+          <t>Bloqueia a estimativa de E06 - T-shirt pode variar de S a XL. Recomenda-se decompor em fase informacional (Fase 1) + transacional (futura) ate o cliente definir casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1701,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>WhatsApp adiciona dependencia externa, custo recorrente e lead time de aprovacao Meta fora do controle. Se nao confirmado, MVP em webchat e WhatsApp fase posterior. Impacta cronograma e custeio.</t>
+          <t>WhatsApp adiciona dependencia externa, custo recorrente e lead time de aprovacao Meta fora do controle. Se nao confirmado, Fase 1 em webchat e WhatsApp fase posterior. Impacta cronograma e custeio.</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2290,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Assunção de faseamento: fundação-antes-de-marketplace com E05 (integração) iniciada mock-first já na Fase 1 — sequenciamento por caminho crítico (E05/E08 → E01 → E02/E03). Válida enquanto o risco #1 for a ausência de contratos de API; se os contratos existirem cedo, a fundação e o marketplace podem paralelizar mais.</t>
+          <t>Assunção de faseamento: fundação-antes-de-marketplace com E05 (integração) iniciada mock-first já na Etapa 1 — sequenciamento por caminho crítico (E05/E08 → E01 → E02/E03). Válida enquanto o risco #1 for a ausência de contratos de API; se os contratos existirem cedo, a fundação e o marketplace podem paralelizar mais.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Valida-se com o inventário de contratos de API na Fase 0. Se a integração deixar de ser o gargalo, o roadmap comprime. Revise se G0501 se resolver.</t>
+          <t>Valida-se com o inventário de contratos de API na Etapa 0. Se a integração deixar de ser o gargalo, o roadmap comprime. Revise se G0501 se resolver.</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2312,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Assunção de faseamento: E09 (Change &amp; Adoção) tem pico na Fase 4, mas a comunicação com as ~600-700 facilitadoras arranca na Fase 1 — a resistência esperada (perda de margem no modelo transparente) exige antecipação. Válida enquanto a fronteira de escopo change PS vs. Dataprev/MTE (G0901/G0906) não for definida.</t>
+          <t>Assunção de faseamento: E09 (Change &amp; Adoção) tem pico na Etapa 4, mas a comunicação com as ~600-700 facilitadoras arranca na Etapa 1 — a resistência esperada (perda de margem no modelo transparente) exige antecipação. Válida enquanto a fronteira de escopo change PS vs. Dataprev/MTE (G0901/G0906) não for definida.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2276,7 +2449,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Premissa scopezilla-recommended, a ratificar com o cliente. Resolve G0504 (hospedagem MuleSoft). Cria três pré-requisitos externos de lead-time na Fase 0 (org greenfield, infra on-premise, gateway) — o maior risco à data fixa de 15/nov. Se a infra atrasar, a data não é alcançável só com esforço.</t>
+          <t>Premissa scopezilla-recommended, a ratificar com o cliente. Resolve G0504 (hospedagem MuleSoft). Cria três pré-requisitos externos de lead-time na Etapa 0 (org greenfield, infra on-premise, gateway) — o maior risco à data fixa de 15/nov. Se a infra atrasar, a data não é alcançável só com esforço.</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2488,56 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Roadmap futuro: qual o CANAL da NOTIFICAÇÃO ATIVA (push) às facilitadoras quando uma beneficiária publica uma demanda/leilão no portal? (e-mail, webhook/evento à API da facilitadora, WhatsApp/BSP, notificação in-app, ou jornada Marketing Cloud). No MVP entregamos apenas endpoint de consulta (pull, G0207); a notificação ativa e a escolha do canal ficam para versão futura.</t>
+          <t>Roadmap futuro: qual o CANAL da NOTIFICAÇÃO ATIVA (push) às facilitadoras quando uma beneficiária publica uma demanda/leilão no portal? (e-mail, webhook/evento à API da facilitadora, WhatsApp/BSP, notificação in-app, ou jornada Marketing Cloud). Na Fase 1 entregamos apenas endpoint de consulta (pull, G0207); a notificação ativa e a escolha do canal ficam para versão futura.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>A escolha do canal é o que DECIDE se posicionamos ou não Marketing Cloud (G0209): um push transacional simples pode sair por webhook/Flow/e-mail nativo sem produto novo; uma jornada rica justificaria Marketing Cloud (licença + configuração). Não dimensionar o push nem somar produto enquanto o canal não for definido com o cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>G0510</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Integração / MuleSoft</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>E05 corre como frente MuleSoft contínua (S1-S11) com UM builder humano (R06, Dev MuleSoft integral) + Arquiteto MuleSoft fracional (R13, 20h/sem no dev) + especialista de pagamentos (R12). Marketplace (S5-10) e Financeiro (S6-11) consomem integração EM PARALELO. O dimensionamento aposta que o lado Marketplace exige só um endpoint de consulta leve (pull, facilitadora API-only), concentrando a carga pesada de MuleSoft no Financeiro.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>⚠ Watch de SUB-escopo (grill 03/ago, re-plano ADR 0006). Se o Marketplace exigir mais que um pull-endpoint OU a integração do gateway PCI escorregar, um único builder vira gargalo na frente de RISCO #1 (sem contratos de API). Alavanca de mitigação conhecida: 2º Dev MuleSoft na sobreposição S6-S11. A confirmar quando os contratos de API/escopo do gateway forem conhecidos na Fundação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>G0511</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Scale / Sustentação</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Scale/Hypercare (S14-S17) cobre os primeiros 4 ciclos reais de produção com 0,5 Consultor Técnico (20h/sem) + 1 Dev MuleSoft integral (40h/sem) + 10h/sem Arquiteto Técnico + 10h/sem Senior PM. Alocação especificada pelo Solution Manager.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>✅ RESOLVIDO no grill 03/ago (APOSTA B). O watch de carga de incidentes foi aceito pelo usuário e mitigado na origem: o Dev MuleSoft do Scale foi reforçado de 0,5 FTE (20h/sem) para 1,0 FTE integral (40h/sem) nas 4 semanas — +80h → Scale 320h, total do programa 5.200h. Justificativa: os primeiros ciclos folha→boleto→split→conciliação sob dinheiro real são o pico de incidência numa plataforma financeira regulada, e um dev integral (não meio-período) cobre esse surge sem depender de acionamento reativo. Propagado a todos os outputs (resource-plan, commercials, estimate-comparison, roadmap, 02-delivery-plan, rom-cliente.html, deal-review.html, presentation-deck.html + PPTX).</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3623,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dado que sou uma facilitadora autenticada na API, Quando chamo o endpoint de consulta de demandas, Então recebo as demandas em janela aberta com seus atributos (funcionários, valor, vigência, distribuição por UF, recursos obrigatórios); Dado que uma demanda já fechou a janela, Quando consulto, Então ela não é retornada como aberta; Dado que não tenho credencial válida, Quando chamo o endpoint, Então recebo erro de autenticação; Dado que o MVP é pull, Quando não consulto, Então não recebo nenhuma notificação ativa (push é roadmap futuro)</t>
+          <t>Dado que sou uma facilitadora autenticada na API, Quando chamo o endpoint de consulta de demandas, Então recebo as demandas em janela aberta com seus atributos (funcionários, valor, vigência, distribuição por UF, recursos obrigatórios); Dado que uma demanda já fechou a janela, Quando consulto, Então ela não é retornada como aberta; Dado que não tenho credencial válida, Quando chamo o endpoint, Então recebo erro de autenticação; Dado que a Fase 1 é pull, Quando não consulto, Então não recebo nenhuma notificação ativa (push é roadmap futuro)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3421,7 +3638,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Endpoint exposto/orquestrado por MuleSoft (E05); notificação push fica fora do MVP.</t>
+          <t>Endpoint exposto/orquestrado por MuleSoft (E05); notificação push fica fora da Fase 1.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3681,7 +3898,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Seleção é manual (não automática por menor taxa) no MVP.</t>
+          <t>Seleção é manual (não automática por menor taxa) na Fase 1.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3869,7 +4086,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Como Facilitadora, após ser selecionada, quero fazer upload de um contrato em PDF imutável com metadados via API, para firmar a contratação sem um módulo de gestão de ciclo de vida de contrato (sem CLM no MVP).</t>
+          <t>Como Facilitadora, após ser selecionada, quero fazer upload de um contrato em PDF imutável com metadados via API, para firmar a contratação sem um módulo de gestão de ciclo de vida de contrato (sem CLM na Fase 1).</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3884,12 +4101,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[KB: salesforce-revenue-cloud-marketplace-arch.md:43] CLM não usado no MVP; ADR 0004 (contrato via upload PDF, sem CLM) [Assumed]</t>
+          <t>[KB: salesforce-revenue-cloud-marketplace-arch.md:43] CLM não usado na Fase 1; ADR 0004 (contrato via upload PDF, sem CLM) [Assumed]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Contrato como objeto nativo/custom com ContentDocument imutável; nenhuma funcionalidade de CLM (redlining, cláusulas, e-signature) no MVP.</t>
+          <t>Contrato como objeto nativo/custom com ContentDocument imutável; nenhuma funcionalidade de CLM (redlining, cláusulas, e-signature) na Fase 1.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3978,7 +4195,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dado que um contrato foi firmado, Quando acesso o termo de aceite, Então informo, por CNPJ, a quantidade de trabalhadores acima e abaixo de 5 salários mínimos; Dado que a soma das faixas não bate com o nº de trabalhadores do CNPJ, Quando submeto, Então recebo aviso de inconsistência; Dado que o termo é dado como MVP-required, Quando concluo, Então o contrato só é considerado apto quando o termo está preenchido</t>
+          <t>Dado que um contrato foi firmado, Quando acesso o termo de aceite, Então informo, por CNPJ, a quantidade de trabalhadores acima e abaixo de 5 salários mínimos; Dado que a soma das faixas não bate com o nº de trabalhadores do CNPJ, Quando submeto, Então recebo aviso de inconsistência; Dado que o termo é dado como Fase 1-required, Quando concluo, Então o contrato só é considerado apto quando o termo está preenchido</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3988,7 +4205,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ADR 0004 (termo de aceite MVP-required, faixa 5 SM); discovery (regra fiscal PAT) [Assumed]</t>
+          <t>ADR 0004 (termo de aceite Fase 1-required, faixa 5 SM); discovery (regra fiscal PAT) [Assumed]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4545,12 +4762,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como Admin da plataforma, quero enriquecer o histórico das facilitadoras com dados do Data Cloud, para dar mais contexto na avaliação de propostas — reconhecendo que este item é candidato a de-escopo no MVP.</t>
+          <t>Como Admin da plataforma, quero enriquecer o histórico das facilitadoras com dados do Data Cloud, para dar mais contexto na avaliação de propostas — reconhecendo que este item é candidato a de-escopo na Fase 1.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dado que o Data Cloud está disponível, Quando visualizo uma facilitadora, Então vejo indicadores de histórico enriquecidos; Dado que o Data Cloud é de-escopado do MVP, Quando o recurso está desligado, Então a comparação de propostas continua funcionando sem enriquecimento; Dado o status Assumed deste item, Quando a decisão de escopo é tomada, Então o requisito é confirmado ou movido para roadmap</t>
+          <t>Dado que o Data Cloud está disponível, Quando visualizo uma facilitadora, Então vejo indicadores de histórico enriquecidos; Dado que o Data Cloud é de-escopado da Fase 1, Quando o recurso está desligado, Então a comparação de propostas continua funcionando sem enriquecimento; Dado o status Assumed deste item, Quando a decisão de escopo é tomada, Então o requisito é confirmado ou movido para roadmap</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4560,7 +4777,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ADR 0004 (Data Cloud para enriquecer histórico — Assumed, candidato a de-escopo) [Assumption: confirmar inclusão no MVP com cliente]</t>
+          <t>ADR 0004 (Data Cloud para enriquecer histórico — Assumed, candidato a de-escopo) [Assumption: confirmar inclusão na Fase 1 com cliente]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4597,12 +4814,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como Facilitadora, quero que a notificação ativa (push) de novas demandas seja reconhecida como roadmap futuro com canal a definir, para que o MVP dependa apenas do modelo pull.</t>
+          <t>Como Facilitadora, quero que a notificação ativa (push) de novas demandas seja reconhecida como roadmap futuro com canal a definir, para que a Fase 1 dependa apenas do modelo pull.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dado que o MVP entrega apenas consulta pull, Quando uma nova demanda é publicada, Então nenhuma notificação push é enviada às facilitadoras; Dado que push é roadmap futuro, Quando o item é planejado, Então o canal (e-mail, webhook, etc.) é definido em fase posterior; Dado que dependo do pull, Quando não consulto o endpoint, Então posso perder a janela — risco documentado</t>
+          <t>Dado que a Fase 1 entrega apenas consulta pull, Quando uma nova demanda é publicada, Então nenhuma notificação push é enviada às facilitadoras; Dado que push é roadmap futuro, Quando o item é planejado, Então o canal (e-mail, webhook, etc.) é definido em fase posterior; Dado que dependo do pull, Quando não consulto o endpoint, Então posso perder a janela — risco documentado</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4612,12 +4829,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ADR 0004 (notificação push é roadmap futuro, canal a definir; MVP é pull) [Assumption]</t>
+          <t>ADR 0004 (notificação push é roadmap futuro, canal a definir; Fase 1 é pull) [Assumption]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Push explicitamente fora do MVP; incluído para rastrear a fronteira de escopo.</t>
+          <t>Push explicitamente fora da Fase 1; incluído para rastrear a fronteira de escopo.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4825,7 +5042,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>As linhas da folha NÃO são carregadas em objeto no MVP — validação opera sobre o arquivo; conjunto de críticas a confirmar</t>
+          <t>As linhas da folha NÃO são carregadas em objeto na Fase 1 — validação opera sobre o arquivo; conjunto de críticas a confirmar</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4862,7 +5079,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dado um conjunto de folhas históricas, quando avalio a abordagem de críticas (regras determinísticas vs. Einstein/agente), então documento fit, precisão esperada e custo; Dado a decisão de arquitetura, quando registro o resultado, então fica claro se a detecção assistida entra no MVP ou é diferida; Dado que a abordagem assistida não entra no MVP, quando processo a folha, então as críticas determinísticas cobrem o mínimo obrigatório</t>
+          <t>Dado um conjunto de folhas históricas, quando avalio a abordagem de críticas (regras determinísticas vs. Einstein/agente), então documento fit, precisão esperada e custo; Dado a decisão de arquitetura, quando registro o resultado, então fica claro se a detecção assistida entra na Fase 1 ou é diferida; Dado que a abordagem assistida não entra na Fase 1, quando processo a folha, então as críticas determinísticas cobrem o mínimo obrigatório</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5085,7 +5302,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Valor a pagar é fornecido pela facilitadora; plataforma não recalcula o valor da folha no MVP</t>
+          <t>Valor a pagar é fornecido pela facilitadora; plataforma não recalcula o valor da folha na Fase 1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5117,7 +5334,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Como plataforma, quero modelar um objeto custom de cabeçalho/competência da folha (sem linhas), para rastrear o ciclo sem carregar os itens da folha no MVP.</t>
+          <t>Como plataforma, quero modelar um objeto custom de cabeçalho/competência da folha (sem linhas), para rastrear o ciclo sem carregar os itens da folha na Fase 1.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5137,7 +5354,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Carga de linhas da folha é necessidade futura, fora do MVP</t>
+          <t>Carga de linhas da folha é necessidade futura, fora da Fase 1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5605,7 +5822,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Teto de 3,6% é o limite regulatório aplicável ao split no MVP</t>
+          <t>Teto de 3,6% é o limite regulatório aplicável ao split na Fase 1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6001,12 +6218,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Como plataforma, quero enviar à CTPS Digital a 'expectativa de crédito' do trabalhador, para monitoramento no MVP, sem gestão de saldo.</t>
+          <t>Como plataforma, quero enviar à CTPS Digital a 'expectativa de crédito' do trabalhador, para monitoramento na Fase 1, sem gestão de saldo.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dado um ciclo com crédito concedido, quando aciono a integração da CTPS Digital, então envio um aviso de 'expectativa de crédito' (modelo similar ao FGTS); Dado que o MVP é só monitoramento, quando envio, então não há gestão de saldo nem consulta de extrato; Dado falha de integração, quando ocorre, então o evento é reenfileirado sem bloquear o ciclo financeiro</t>
+          <t>Dado um ciclo com crédito concedido, quando aciono a integração da CTPS Digital, então envio um aviso de 'expectativa de crédito' (modelo similar ao FGTS); Dado que a Fase 1 é só monitoramento, quando envio, então não há gestão de saldo nem consulta de extrato; Dado falha de integração, quando ocorre, então o evento é reenfileirado sem bloquear o ciclo financeiro</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6016,12 +6233,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>'via CTPS Digital (expectativa de crédito, só monitoramento no MVP)' [.discovery-context.md]; CTPS Digital [L26]</t>
+          <t>'via CTPS Digital (expectativa de crédito, só monitoramento na Fase 1)' [.discovery-context.md]; CTPS Digital [L26]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Escopo CTPS no MVP restrito a aviso/monitoramento; contrato de integração a confirmar</t>
+          <t>Escopo CTPS na Fase 1 restrito a aviso/monitoramento; contrato de integração a confirmar</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6697,7 +6914,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Sem base nacional de vigilância sanitária; integração direta com órgãos sanitários é ideal futuro, não garantido no MVP.</t>
+          <t>Sem base nacional de vigilância sanitária; integração direta com órgãos sanitários é ideal futuro, não garantido na Fase 1.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7113,7 +7330,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Portal do estabelecimento não exibe repasses financeiros no MVP (fica com adquirente).</t>
+          <t>Portal do estabelecimento não exibe repasses financeiros na Fase 1 (fica com adquirente).</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7913,12 +8130,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Como plataforma, quero enviar à CTPS Digital a 'expectativa de crédito' ao trabalhador (apenas monitoramento no MVP), para notificar o trabalhador de forma análoga ao aviso de crédito do FGTS.</t>
+          <t>Como plataforma, quero enviar à CTPS Digital a 'expectativa de crédito' ao trabalhador (apenas monitoramento na Fase 1), para notificar o trabalhador de forma análoga ao aviso de crédito do FGTS.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dado um crédito processado para uma folha, Quando o evento é gerado, Então uma notificação de expectativa de crédito é enviada à CTPS Digital (sem gestão de saldo); Dado o MVP, Quando avalio o escopo, Então é apenas envio/monitoramento — não há débito, gestão de saldo nem transação financeira via CTPS; Dado indisponibilidade da CTPS, Quando o envio falha, Então o evento entra em reprocessamento sem impactar o crédito</t>
+          <t>Dado um crédito processado para uma folha, Quando o evento é gerado, Então uma notificação de expectativa de crédito é enviada à CTPS Digital (sem gestão de saldo); Dado a Fase 1, Quando avalio o escopo, Então é apenas envio/monitoramento — não há débito, gestão de saldo nem transação financeira via CTPS; Dado indisponibilidade da CTPS, Quando o envio falha, Então o evento entra em reprocessamento sem impactar o crédito</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7928,12 +8145,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>discovery-context 00 (notificação ao trabalhador via CTPS Digital, modelo similar ao FGTS — aviso de crédito, não gestão de saldo); E05 (só monitoramento no MVP)</t>
+          <t>discovery-context 00 (notificação ao trabalhador via CTPS Digital, modelo similar ao FGTS — aviso de crédito, não gestão de saldo); E05 (só monitoramento na Fase 1)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Contrato CTPS Digital não disponível — mock-first; escopo MVP limitado a notificação</t>
+          <t>Contrato CTPS Digital não disponível — mock-first; escopo Fase 1 limitado a notificação</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7985,7 +8202,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Escopo exato do consumo de eSocial no MVP a confirmar</t>
+          <t>Escopo exato do consumo de eSocial na Fase 1 a confirmar</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -8193,7 +8410,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Push/webhook em tempo real fora do MVP — batch agendado é a decisão</t>
+          <t>Push/webhook em tempo real fora da Fase 1 — batch agendado é a decisão</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -8282,7 +8499,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dado cotações abertas dentro do prazo, Quando a facilitadora chama o endpoint de consulta, Então recebe a lista de demandas abertas com nº de funcionários, valor, UF e prazo; Dado uma cotação fora da vigência/prazo, Quando a consulta é feita, Então ela não aparece na lista; Dado o MVP, Quando avalio o modelo, Então é pull (a facilitadora consulta) — push é roadmap futuro</t>
+          <t>Dado cotações abertas dentro do prazo, Quando a facilitadora chama o endpoint de consulta, Então recebe a lista de demandas abertas com nº de funcionários, valor, UF e prazo; Dado uma cotação fora da vigência/prazo, Quando a consulta é feita, Então ela não aparece na lista; Dado a Fase 1, Quando avalio o modelo, Então é pull (a facilitadora consulta) — push é roadmap futuro</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8292,7 +8509,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>E05 (EXPOSIÇÃO DE ENDPOINT DE CONSULTA das demandas/leilões abertos — pull no MVP; push é roadmap futuro)</t>
+          <t>E05 (EXPOSIÇÃO DE ENDPOINT DE CONSULTA das demandas/leilões abertos — pull na Fase 1; push é roadmap futuro)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -8429,12 +8646,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Como facilitadora, quero (roadmap futuro) receber push de notificação de novas demandas, para reagir mais rápido do que no modelo pull do MVP.</t>
+          <t>Como facilitadora, quero (roadmap futuro) receber push de notificação de novas demandas, para reagir mais rápido do que no modelo pull da Fase 1.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dado o MVP, Quando avalio o escopo, Então push NÃO está incluído (apenas pull); Dado o roadmap, Quando push for priorizado, Então uma facilitadora poderá registrar um endpoint/callback para receber notificações de novas demandas; Dado o design MVP, Quando construo o endpoint de consulta, Então ele não impede a evolução para push (não cria dependência que bloqueie)</t>
+          <t>Dado a Fase 1, Quando avalio o escopo, Então push NÃO está incluído (apenas pull); Dado o roadmap, Quando push for priorizado, Então uma facilitadora poderá registrar um endpoint/callback para receber notificações de novas demandas; Dado o design Fase 1, Quando construo o endpoint de consulta, Então ele não impede a evolução para push (não cria dependência que bloqueie)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8449,7 +8666,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Push explicitamente fora do MVP</t>
+          <t>Push explicitamente fora da Fase 1</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8586,7 +8803,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dado o MVP/near-term, Quando avalio o escopo, Então analytics completo NÃO está incluído (apenas ingestão para consulta); Dado o roadmap V2, Quando for priorizado, Então as transações ingeridas alimentarão análise de padrões (ex.: Data Cloud/Tableau, a reavaliar); Dado o design de ingestão near-term, Quando o construo, Então o modelo de dados suporta a evolução para analytics sem reingestão</t>
+          <t>Dado a Fase 1/near-term, Quando avalio o escopo, Então analytics completo NÃO está incluído (apenas ingestão para consulta); Dado o roadmap V2, Quando for priorizado, Então as transações ingeridas alimentarão análise de padrões (ex.: Data Cloud/Tableau, a reavaliar); Dado o design de ingestão near-term, Quando o construo, Então o modelo de dados suporta a evolução para analytics sem reingestão</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9462,7 +9679,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dado o provisionamento, quando o ambiente é criado, então nenhum metadado, perfil ou configuração é herdado de outras orgs Dataprev; Dada a administração, quando papéis de admin são atribuídos, então não há administração compartilhada com outros ambientes; Dado o marco de prontidão da Fase 0, quando a org greenfield é entregue, então ela é validada como isolada antes do início do build; Dado o lead-time externo, quando o provisionamento é planejado, então é tratado como pré-requisito de marco</t>
+          <t>Dado o provisionamento, quando o ambiente é criado, então nenhum metadado, perfil ou configuração é herdado de outras orgs Dataprev; Dada a administração, quando papéis de admin são atribuídos, então não há administração compartilhada com outros ambientes; Dado o marco de prontidão da Etapa 0, quando a org greenfield é entregue, então ela é validada como isolada antes do início do build; Dado o lead-time externo, quando o provisionamento é planejado, então é tratado como pré-requisito de marco</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9514,7 +9731,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dado o deploy do MuleSoft, quando a topologia é definida, então o runtime roda on-premise na infra Dataprev/gov, não em CloudHub; Dado que a de-tokenização do CPF ocorre, quando ela é executada, então acontece dentro do perímetro soberano; Dada a prontidão da infra, quando o MuleSoft on-premise é instalado, então é pré-requisito de marco na Fase 0 com lead-time externo mapeado; Dado o trânsito de dados, quando dado sensível é resolvido, então ele não trafega por infraestrutura fora do perímetro soberano</t>
+          <t>Dado o deploy do MuleSoft, quando a topologia é definida, então o runtime roda on-premise na infra Dataprev/gov, não em CloudHub; Dado que a de-tokenização do CPF ocorre, quando ela é executada, então acontece dentro do perímetro soberano; Dada a prontidão da infra, quando o MuleSoft on-premise é instalado, então é pré-requisito de marco na Etapa 0 com lead-time externo mapeado; Dado o trânsito de dados, quando dado sensível é resolvido, então ele não trafega por infraestrutura fora do perímetro soberano</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11156,17 +11373,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arranque, Provisionamento &amp; Arquitetura (17/ago – 30/ago · Sem. 1-2)</t>
+          <t>Fundação — Arquitetura + Planning &amp; Design + Modelo de Dados + Identidade + Integração + Residência (17/ago – 13/set · Sem. 1-4)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11176,40 +11393,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Início em 17/ago/2026. Destravar os pré-requisitos de arranque que têm lead-time externo e competem com a janela fixa: (1) provisionamento da INSTÂNCIA DEDICADA E APARTADA do MTE/PAT em ambiente 100% GREENFIELD (ADR 0002/0005) — pedido junto ao fornecedor/plataforma tem prazo próprio; (2) INFRAESTRUTURA MuleSoft ON-PREMISE pronta e acessível (ADR 0005) — instalação na infra soberana Dataprev/gov, pré-requisito de marco; (3) SELEÇÃO DO PROVEDOR DO GATEWAY / banco custódia (G0309, ADR 0003) — contratação de terceiro no caminho crítico do financeiro; (4) os blockers de arquitetura: fronteira campo-a-campo da residência híbrida (G0801, ratificar com Jair Bogo), inventário de contratos/Swaggers de API dos sistemas externos (G0501, Novo PAT sem API hoje), identidade Experience Cloud Partner Community × CPF-não-persiste (G0106). Iniciar engajamento CTID/ANPD e inventário das APIs das facilitadoras.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Início em 17/ago/2026 NA SEMANA 1 — a Definição de Arquitetura foi MESCLADA ao Planning &amp; Design desta etapa (não há mais uma Etapa 0 de aprovisionamento). Isso é possível porque o MuleSoft NÃO é mais uma nova instância greenfield: REUSA a instalação on-premise existente na infra soberana Dataprev/gov (ADR 0006, supera ADR 0005) — elimina o lead-time de provisionamento da camada de integração e as duas semanas iniciais. ARRANCAR COM O TIME DE IMPLEMENTAÇÃO INTEIRO (ADR 0004): (1) fechar a arquitetura e o Planning &amp; Design junto com a DEFINIÇÃO FUNDACIONAL DE OBJETOS E MAPEAMENTO DE DADOS — o modelo de dados Sales Cloud nativo (Account = beneficiária/CNPJ; Opportunity = demanda do leilão reverso; Quote = resposta da facilitadora via API; termo de aceite/faixa salarial; matriz/filial) é a base compartilhada de que TODAS as frentes dependem; (2) subir o hub de integração sobre o MuleSoft on-premise REUSADO, mock-first (E05 — risco #1, começado na Sem. 1, já com o gateway como alvo; Novo PAT sem API mantém mock obrigatório) — E05 abre como FRENTE CONTÍNUA que se estende por todo o P&amp;D e DEV (Sem. 1-11); (3) o modelo de residência/tokenização (E08 — soberania, dado sensível não sai do perímetro on-premise); (4) o portal Experience Cloud PARTNER COMMUNITY com login gov.br (E01). Em paralelo (responsabilidade do cliente, day-1, sem gatear a Fundação): provisionamento da instância Salesforce dedicada greenfield (ADR 0002) e seleção/contratação do provedor do gateway PCI (G0309). Iniciar a comunicação de mudança (E09 arranca aqui).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>E05,E08,E01</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Org dedicada greenfield provisionada e acessível; MuleSoft on-premise instalado e acessível na infra soberana; provedor do gateway selecionado/contratação iniciada com escopo de integração acordado; ADR 0001 ratificado com fronteira campo-a-campo definida; inventário de contratos de API por sistema (existe/não existe). MARCO DE PROJETO: kick-off e ambiente pronto ao fim da Sem. 2.</t>
+          <t>Arquitetura e Planning &amp; Design fechados; MODELO DE DADOS FUNDACIONAL definido e ratificado com o time inteiro (objetos nativos Opportunity/Quote/Account + termo de aceite) — MARCO que libera a paralelização das frentes; camada API-led sobre o MuleSoft on-premise REUSADO de pé com mocks (incluindo o contrato de integração com o gateway); modelo de referência tokenizada resolvendo em runtime; portal Partner Community com login gov.br funcional. Base pronta para as frentes paralelas de Marketplace e Financeiro. MARCO DE PROJETO ao fim da Sem. 4 (13/set).</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nenhuma — é a fase que precede tudo. Requer disponibilidade da arquitetura Dataprev (Jair Bogo), dos donos dos sistemas externos, a INFRA (org + MuleSoft on-premise) pronta nos marcos, e a decisão do cliente sobre o provedor do gateway.</t>
+          <t>Nenhuma etapa anterior (a antiga Etapa 0 de aprovisionamento foi eliminada). Requer disponibilidade da arquitetura Dataprev (Jair Bogo), dos donos dos sistemas externos, e o ACESSO à instalação MuleSoft on-premise existente (reuso — sem lead-time de provisionamento). Provisionamento da org dedicada e contratação do gateway correm em paralelo como ação do cliente e não gateiam o arranque, mas gateiam a ida do Financeiro a produção.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PROVISIONAMENTO DA ORG + INFRA MuleSoft ON-PREMISE + CONTRATAÇÃO DO GATEWAY SÃO O MAIOR RISCO À DATA FIXA — três lead-times de terceiros que consomem a janela e não estão sob controle da entrega. Se qualquer um atrasar além da Fase 0, o go-live de 15/nov fica em risco e o financeiro (E03) é o primeiro candidato a fatiar. Se a infra on-premise não estiver pronta no marco, a Fundação não arranca. Novo PAT sem API mantém E05 mock-first — caminho crítico aberto.</t>
+          <t>Sem o MuleSoft on-premise como lead-time externo (agora reuso — ADR 0006), o maior risco à data fixa recua para: (a) a definição do modelo de dados fundacional fechar cedo (gargalo de sequenciamento — nada paraleliza antes); (b) ausência de contratos de API (G0501, Novo PAT sem API) que trava a virada mock→real; (c) provisionamento da org dedicada e contratação do gateway (ação do cliente em paralelo) chegarem a tempo para o Financeiro. Adaptar objetos nativos sell-side (Opportunity/Quote) ao padrão comprador→N-vendedores adiciona esforço (ADR 0004). Janela de 4 semanas iniciando na Sem. 1 dá mais prazo às frentes de DEV e REDUZ o risco de cronograma vs. o plano anterior.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fundação — Modelo de Dados + Identidade + Integração + Residência (31/ago – 27/set · Sem. 3-6)</t>
+          <t>Marketplace &amp; Credenciamento — Frente Paralela (14/set – 25/out · Sem. 5-10 · 2 sprints de 3 semanas)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11219,44 +11440,44 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ARRANCAR COM A DEFINIÇÃO FUNDACIONAL DE OBJETOS E MAPEAMENTO DE DADOS, COM O TIME DE IMPLEMENTAÇÃO INTEIRO (ADR 0004, premissa de arranque) — o modelo de dados Sales Cloud nativo (Account = beneficiária/CNPJ; Opportunity = demanda do leilão reverso; Quote = resposta da facilitadora via API; termo de aceite/faixa salarial; matriz/filial) é a base compartilhada de que TODAS as frentes dependem. Só depois de o modelo estar acordado é que as frentes de baixa/nenhuma dependência PARALELIZAM — a paralelização é a estratégia que torna a data fixa viável. Sobre essa base: hub de integração MuleSoft ON-PREMISE mock-first (E05 — o risco #1, começado cedo, já com o gateway como alvo; Novo PAT sem API mantém mock obrigatório), o modelo de residência/tokenização (E08 — greenfield + soberania, ADR 0005) que governa o data model das demais épicas, e o portal Experience Cloud PARTNER COMMUNITY com login gov.br (E01). Iniciar a comunicação de mudança com as facilitadoras (E09 arranca aqui, mesmo com pico depois).</t>
+          <t>FRENTE PARALELIZADA sobre o modelo de dados fundacional da Fundação, agora com JANELA MAIS LONGA (6 semanas = 2 sprints de 3 semanas), o que reduz o risco de cronograma. Construir o valor mais visível da reforma sobre objetos nativos Sales Cloud (ADR 0004): o leilão reverso (E02 — beneficiária cadastra a demanda como Opportunity → facilitadoras respondem com Quote via API, ocultas até o fechamento → comparação lado a lado → seleção manual → contrato SEM CLM, PDF imutável versionado) e o credenciamento unificado de estabelecimentos (E04 — com vigilância sanitária + consulta à adquirente via API). E02 e E04 correm em paralelo por terem baixa dependência entre si. Fase 1 de E02 SEM Data Cloud (enriquecimento é de-escopo/buffer).</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>E05,E08,E01</t>
+          <t>E02,E04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MODELO DE DADOS FUNDACIONAL definido e ratificado com o time inteiro (objetos nativos Opportunity/Quote/Account + termo de aceite) — MARCO que libera a paralelização das demais frentes; camada API-led MuleSoft on-premise de pé com mocks (incluindo o contrato de integração com o gateway); modelo de referência tokenizada implementado e resolvendo em runtime na org greenfield dedicada; portal Partner Community com login gov.br funcional e Contact por referência tokenizada. Base pronta para o marketplace.</t>
+          <t>MARCO DE ENTREGA DE JORNADA: beneficiária publica a demanda (Opportunity), facilitadoras enviam Quotes via API (ocultas até o fechamento), tela 'Comparar Propostas' operante, seleção manual registra o vencedor; estabelecimentos se credenciam via gov.br PJ (CNPJ) com aprovação da facilitadora e checagem de vigilância sanitária. A ENTREGA DA FRENTE MARKETPLACE ABRE O UAT (a partir da Sem. 8). Capacidades principais: leilão reverso + credenciamento.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fase 0 (org greenfield provisionada, MuleSoft on-premise instalado, blockers resolvidos, gateway selecionado). A definição fundacional do modelo de dados É o pré-requisito interno que precede a paralelização de E02/E04 na Fase 2. E01 depende de E05 (resolução de identidade) e E08 (Contact tokenizado).</t>
+          <t>Fundação (modelo de dados fundacional ratificado — habilitador da paralelização; E01 portal/identidade Partner Community, E05 integração on-premise reusada). E02 e E04 dependem de E01 + E05; entre si, baixa dependência (paralelizáveis).</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Se o modelo de dados fundacional não fechar cedo, a paralelização não arranca e a data fixa fica em risco — é o gargalo de sequenciamento interno. Ausência de contratos de API (G0501, Novo PAT sem API) trava a virada mock→real; fronteira de residência (G0801) não ratificada re-molda o data model; conector gov.br OIDC nativo inexistente (G0101); adaptar objetos nativos sell-side (Opportunity/Quote) ao padrão comprador→N-vendedores adiciona esforço (ADR 0004). Fase de maior carga dentro da janela mais apertada da história do projeto.</t>
+          <t>Regras de seleção/desempate e conformidade Lei 14.133/2021 indefinidas (G0202/G0203); tela de comparação ausente no protótipo (G0201); conflito de system-of-record do credenciamento (G0401); 5000+ padrões municipais de vigilância sanitária (extração IA + transbordo humano). Data Cloud para enriquecimento fica FORA da Fase 1 — buffer de cronograma. A janela de 6 semanas (2 sprints) absorve melhor a incerteza de regras que a janela anterior de 3 semanas.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marketplace &amp; Credenciamento — Frentes Paralelas (28/set – 18/out · Sem. 7-9)</t>
+          <t>Financeiro — Folha, Motor de Split &amp; Conciliação — Frente Paralela (21/set – 01/nov · Sem. 6-11)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11266,44 +11487,44 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FRENTE PARALELIZADA sobre o modelo de dados fundacional da Fase 1 (premissa de paralelização). Construir o valor mais visível da reforma sobre objetos nativos Sales Cloud (ADR 0004): o leilão reverso (E02 — beneficiária cadastra a demanda como Opportunity → facilitadoras respondem com Quote via API, ocultas até o fechamento → comparação lado a lado → seleção manual → contrato SEM CLM, PDF imutável versionado) e o credenciamento unificado de estabelecimentos (E04 — com vigilância sanitária + consulta à adquirente via API). E02 e E04 correm em paralelo por terem baixa dependência entre si. MVP de E02 SEM Data Cloud (enriquecimento é de-escopo/buffer).</t>
+          <t>FRENTE PARALELA, iniciando junto com o Marketplace (Sem. 6, uma semana após o arranque da frente Marketplace) e correndo por 6 semanas até a Sem. 11 — o paralelismo dá ao núcleo regulatório XL uma janela maior e reduz o risco da data fixa. Fechar o núcleo regulatório da reforma (E03, XL — ADR 0003), seguindo o fluxo folha→pagamento→split detalhado: (1) upload da folha por portal/API → plataforma VALIDA layout + integridade; (2) análise de crítica pela melhor alternativa Salesforce (Einstein/agente) — se não houver, disponibiliza o arquivo para download da facilitadora (SEM persistir as linhas da folha em objeto — roadmap futuro); (3) facilitadora baixa a folha por contrato/mês-ano de vigência, devolve status 'processado' + valor a pagar via API; (4) plataforma envia o valor ao GATEWAY (intermedia conta custódia), recebe boleto registrado + metadados/link; (5) boleto disponível à beneficiária no portal; (6) plataforma recebe movimentações bancárias do gateway, identifica o pagamento em LOTES INCREMENTAIS via agendamento MuleSoft; (7) consulta regras de cálculo de split → calcula repasse à facilitadora + demais; (8) registra toda a memória de cálculo/datas/rateio/ordens de transferência e entrega, via MuleSoft, ao GATEWAY (executor único das transações bancárias). O Salesforce é o MOTOR DE REGRAS (teto MDR 3,6%, repasse ≤15 dias — Decreto 12.712/2025); execução bancária e custódia ficam FORA (gateway).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>E02,E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MARCO DE ENTREGA DE JORNADA (UAT): beneficiária publica a demanda (Opportunity), facilitadoras enviam Quotes via API (ocultas até o fechamento), tela 'Comparar Propostas' operante, seleção manual registra o vencedor; estabelecimentos se credenciam via gov.br PJ (CNPJ) com aprovação da facilitadora e checagem de vigilância sanitária. Capacidades principais: leilão reverso + credenciamento.</t>
+          <t>MARCO DE ENTREGA DE JORNADA (para UAT): upload de folha → validação de layout/integridade → crítica → download pela facilitadora → 'processado'+valor via API → gateway emite boleto registrado → beneficiária vê o boleto no portal → conciliação por lotes incrementais via MuleSoft → motor calcula o split → ordens de transferência entregues ao gateway com trilha e idempotência; UI simplificada a status consolidado 'crédito concedido'. Capacidade principal: fluxo financeiro folha→boleto→conciliação→split completo. A entrega alimenta o UAT contínuo (Sem. 8-13).</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fase 1 (modelo de dados fundacional ratificado — habilitador da paralelização; E01 portal/identidade Partner Community, E05 integração on-premise). E02 e E04 dependem de E01 + E05; entre si, baixa dependência (paralelizáveis).</t>
+          <t>Gateway selecionado (ação do cliente em paralelo desde a Sem. 1 — dependência dura para produção), Fundação (E05 integração on-premise reusada com o gateway, E08 residência/soberania). E03 depende de E01 + E05 + E08 + o gateway contratado.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Regras de seleção/desempate e conformidade Lei 14.133/2021 indefinidas (G0202/G0203); tela de comparação ausente no protótipo (G0201); conflito de system-of-record do credenciamento (G0401); 5000+ padrões municipais de vigilância sanitária (extração IA + transbordo humano). Data Cloud para enriquecimento fica FORA do MVP — buffer de cronograma.</t>
+          <t>Provedor do gateway não definido a tempo (G0309) é o risco #1 desta fase — sem o parceiro contratado e integrado, o financeiro não vai a produção em 15/nov; regras de conciliação/divergência por lote incremental ainda indefinidas (G0304); mecânica boleto/Pix e settlement (G0302/G0301). A janela de 6 semanas em paralelo (vs. 3 sequenciais no plano anterior) é a principal alavanca de redução de risco desta frente XL.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financeiro — Folha, Motor de Split &amp; Conciliação (19/out – 8/nov · Sem. 10-12)</t>
+          <t>Homologação (UAT contínuo), Carga Mínima, Adoção &amp; Go-live PROD (UAT Sem. 8-13 · Carga Sem. 12-13 · Go-live 15/nov)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11313,46 +11534,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fechar o núcleo regulatório da reforma (E03, XL — ADR 0003), seguindo o fluxo folha→pagamento→split detalhado (premissa 6): (1) upload da folha por portal/API → plataforma VALIDA layout + integridade ('não quebrada'); (2) análise de crítica pela melhor alternativa Salesforce (Einstein/agente) — se não houver, disponibiliza o arquivo para download da facilitadora (SEM persistir as linhas da folha em objeto — roadmap futuro); (3) facilitadora baixa a folha por contrato/mês-ano de vigência, devolve status 'processado' + valor a pagar via API; (4) plataforma envia o valor ao GATEWAY (intermedia conta custódia), recebe boleto registrado + metadados/link; (5) boleto disponível à beneficiária no portal; (6) plataforma recebe movimentações bancárias do gateway, identifica o pagamento em LOTES INCREMENTAIS via agendamento MuleSoft; (7) consulta regras de cálculo de split → calcula repasse à facilitadora + demais; (8) registra toda a memória de cálculo/datas/rateio/ordens de transferência e entrega, via MuleSoft, ao GATEWAY (executor único das transações bancárias). O Salesforce é o MOTOR DE REGRAS (teto MDR 3,6%, repasse ≤15 dias — Decreto 12.712/2025); execução bancária e custódia ficam FORA (gateway, contratado pelo cliente).</t>
+          <t>UAT/HOMOLOGAÇÃO CONTÍNUO iniciando na Sem. 8 (a partir da entrega da frente Marketplace, o que ANTECIPA o UAT e o estende por 6 semanas, Sem. 8-13 — +1 semana vs. o plano anterior) e recebendo as jornadas de Marketplace e Financeiro à medida que entregam. CARGA MÍNIMA em 2 SEMANAS (Sem. 12-13, as duas últimas — não apenas 1): popular a plataforma com a carga inicial mínima necessária ao go-live (E07 — beneficiárias, facilitadoras e estabelecimentos a partir do Novo PAT/MTE; Novo PAT permanece system-of-record). Conduzir a adoção enxuta (E09 — capacitação e materiais essenciais, com o pico da comunicação já iniciado na Fundação) e virar para PRODUÇÃO em 15/nov/2026. MARCOS: (projeto) go-live PROD 15/nov; (decreto) entrada em vigor da reforma do PAT — Decreto 12.712/2025; (jornada UAT→PROD) portal/identidade, leilão reverso, credenciamento e fluxo financeiro folha→boleto→split disponíveis.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E07,E09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MARCO DE ENTREGA DE JORNADA (UAT/homologação): upload de folha → validação de layout/integridade → crítica → download pela facilitadora → 'processado'+valor via API → gateway emite boleto registrado → beneficiária vê o boleto no portal → conciliação por lotes incrementais via MuleSoft → motor calcula o split → ordens de transferência entregues ao gateway com trilha e idempotência; UI simplificada a status consolidado 'crédito concedido'. Capacidade principal: fluxo financeiro folha→boleto→conciliação→split completo. HOMOLOGAÇÃO INÍCIO NOVEMBRO abre ao fim desta fase.</t>
+          <t>HOMOLOGAÇÃO (UAT contínuo Sem. 8-13) concluída sobre as jornadas entregues (portal, marketplace, credenciamento, financeiro); cadastros mínimos carregados com dedup nas 2 semanas de carga (Sem. 12-13); facilitadoras e beneficiárias com capacitação essencial; GO-LIVE PROD 15/nov estabilizado. Capacidades principais em PROD: identidade gov.br, leilão reverso, credenciamento, financeiro folha→boleto→conciliação→split.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fase 0 (gateway selecionado — dependência dura), Fase 1 (E05 integração on-premise com o gateway, E08 residência/soberania). E03 depende de E01 + E05 + E08 + o gateway contratado.</t>
+          <t>Fundação (E05 para extração/carga). E07 depende de E05. E09 é transversal — sua comunicação começa na Fundação e culmina aqui. O UAT depende das entregas incrementais das frentes Marketplace (Sem. 8+) e Financeiro (Sem. 11).</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Provedor do gateway não definido a tempo (G0309) é o risco #1 desta fase — sem o parceiro contratado e integrado, o financeiro não vai a produção em 15/nov; regras de conciliação/divergência por lote incremental ainda indefinidas (G0304); mecânica boleto/Pix e settlement (G0302/G0301); a crítica da folha depende de qual alternativa Salesforce (Einstein/agente) se confirma viável. É a fase XL mais sensível à data fixa; se algo escorregar, é aqui que a pressão de de-escopo bate.</t>
+          <t>A antecipação do UAT (Sem. 8) e sua extensão para 6 semanas, somadas à carga mínima em 2 semanas (Sem. 12-13) e à eliminação do lead-time do MuleSoft (reuso), tornam a data de 15/nov MENOS agressiva que no plano anterior. Riscos remanescentes: provisionamento da org e contratação do gateway (ação do cliente) chegarem a tempo; volume de carga desconhecido (G0701, ~450k) — mitigado por carga mínima em 2 semanas; resistência das facilitadoras (perda de margem no modelo transparente). Adoção completa e carga massiva ficam pós-go-live e são cobertas pelo Scale/Hypercare.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Scale / Hypercare — Sustentação, Manutenção &amp; Cutover (16/nov – 13/dez · Sem. 14-17 · 4 semanas)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Homologação, Carga Mínima, Adoção &amp; Go-live PROD (9/nov – 15/nov · Sem. 13)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>user</t>
@@ -11360,39 +11581,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fechar a HOMOLOGAÇÃO (UAT) aberta início de novembro e virar para PRODUÇÃO em 15/nov/2026. Popular a plataforma com a carga inicial MÍNIMA necessária ao go-live (E07 — beneficiárias, facilitadoras e estabelecimentos a partir do Novo PAT/MTE; Novo PAT permanece system-of-record), conduzir a adoção enxuta (E09 — capacitação e materiais essenciais, com o pico da comunicação já iniciado na Fase 1) e estabilizar/hypercare até o marco de PROD. MARCOS: (projeto) go-live PROD 15/nov; (decreto) entrada em vigor da reforma do PAT — Decreto 12.712/2025; (jornada UAT→PROD) portal/identidade, leilão reverso, credenciamento e fluxo financeiro folha→boleto→split disponíveis nos dois ambientes.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>E07,E09</t>
-        </is>
-      </c>
+          <t>4 semanas de Scale/Hypercare A PARTIR DE 16/nov/2026 (dia seguinte ao go-live), com uma equipe enxuta cujas responsabilidades são EXCLUSIVAMENTE: SUSTENTAR a operação em produção (monitorar, triar e corrigir incidentes de estabilização), MANTER a plataforma e as integrações on-premise (ajustes finos, saúde das rotas MuleSoft, conciliação/split em produção) e conduzir o CUTOVER (virada operacional completa, escalonamento da carga pós-mínima e handover à operação Dataprev). NÃO há build de nova funcionalidade no Scale — é janela de estabilização, não de escopo novo. Equipe: meio Consultor Técnico (0,5 FTE = 20h/sem), UM Dev MuleSoft integral (1,0 FTE = 40h/sem — reforçado de 0,5 para 1,0 no grill de 03/ago, dado o pico de incidência dos primeiros ciclos financeiros reais sob dinheiro real), 10h/sem de um Arquiteto Técnico e 10h/sem de um Senior PM, nas 4 semanas.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOMOLOGAÇÃO (UAT) concluída sobre as jornadas entregues (portal, marketplace, credenciamento, financeiro); cadastros mínimos carregados com dedup; facilitadoras e beneficiárias com capacitação essencial; GO-LIVE PROD 15/nov estabilizado com hypercare ativo. Capacidades principais em PROD: identidade gov.br, leilão reverso, credenciamento, financeiro folha→boleto→conciliação→split.</t>
+          <t>Operação estável em produção (incidentes de estabilização decrescentes); integrações on-premise saudáveis; conciliação e split rodando em regime; cutover concluído e operação transferida à Dataprev ao fim da Sem. 17 (13/dez).</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fase 1 (E05 para extração/carga). E07 depende de E05. E09 é transversal — sua comunicação começa na Fase 1 e culmina aqui. A homologação depende do encerramento das jornadas da Fase 2 e 3.</t>
+          <t>Go-live PROD 15/nov (Etapa 4 concluída). Reusa recursos-chave do build (Arquiteto Técnico, Senior PM, Consultor Técnico, Dev MuleSoft) em alocação fracional — não é novo headcount.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>⚠ VIABILIDADE DA DATA FIXA — SINALIZAR: 13 semanas para um build XL regulado (financeiro com split, conciliação e emissão de boleto) sobre 3 pré-requisitos externos de lead-time (org greenfield, MuleSoft on-premise, gateway) é um cronograma AGRESSIVO com margem mínima. A janela de estabilização de 1 semana entre o fim do build (8/nov), a homologação e o PROD (15/nov) é o ponto mais frágil: se qualquer pré-requisito da Fase 0 atrasar, ou a homologação achar defeito no financeiro, a data de 15/nov não é alcançável com esforço adicional — nesse caso o de-escopo (E03 financeiro é o primeiro candidato, adiando parte do split/conciliação para pós-go-live) é o único trilho para preservar a data. Volume de carga desconhecido (G0701, ~450k) pode estourar a janela; resistência das facilitadoras (perda de margem no modelo transparente). Adoção completa e carga massiva ficam pós-go-live (buffer).</t>
+          <t>Escopo do Scale estritamente limitado a sustentar/manter/cutover; qualquer nova funcionalidade é roadmap/Fase 2, não Scale. Volume de carga massiva pós-go-live pode pressionar a janela de 4 semanas — o cutover prioriza a estabilidade do fluxo financeiro regulado.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Onda 2 — Pós-MVP (FORA do escopo do go-live 15/nov/2026) — Atendimento Inteligente (Agentforce)</t>
+          <t>Onda 2 — Fase 2 (FORA do escopo do go-live 15/nov/2026) — Atendimento Inteligente (Agentforce)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11407,7 +11624,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atendimento Inteligente com Agentforce (agente informacional e transacional em WhatsApp/webchat para beneficiárias, facilitadoras e estabelecimentos) — DEFERIDO para onda futura após o go-live do MVP. Fora do escopo comprometido de 15/nov/2026; retido como buffer de cronograma da janela fixa. Canais, casos de uso (informacional vs. transacional) e integração com o marketplace a confirmar com o cliente antes de dimensionar a onda.</t>
+          <t>Atendimento Inteligente com Agentforce (agente informacional e transacional em WhatsApp/webchat para beneficiárias, facilitadoras e estabelecimentos) — DEFERIDO para onda futura após o go-live da Fase 1 e o Scale/Hypercare. Fora do escopo comprometido de 15/nov/2026. Canais, casos de uso (informacional vs. transacional) e integração com o marketplace a confirmar com o cliente antes de dimensionar a onda.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -11417,12 +11634,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Escopo do Agentforce ratificado com o cliente (canais, casos de uso, integração) e agente em produção atendendo participantes em escala — em onda posterior, sem impacto na data fixa do MVP.</t>
+          <t>Escopo do Agentforce ratificado com o cliente (canais, casos de uso, integração) e agente em produção atendendo participantes em escala — em onda posterior, sem impacto na data fixa da Fase 1.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MVP em produção (Fase 4 concluída); E05 (hub de integração) e E08 (residência/tokenização) estáveis em produção. Onda não iniciada dentro das 13 semanas comprometidas.</t>
+          <t>Fase 1 em produção (Etapa 4 concluída) e Scale/Hypercare (Etapa 5) encerrados; E05 (hub de integração on-premise) e E08 (residência/tokenização) estáveis em produção.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -11442,7 +11659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11525,12 +11742,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Project/Program Manager</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11555,7 +11772,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11566,7 +11783,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Roster da trilha comprometida (âncora AI-native), copiado de estimate-comparison.json na aprovação do Solution Lead. Accountability única de entrega e da relação MTE×Dataprev; caminho crítico de coordenação (trabalho só-humano). Full-time todo o programa. Janela FIXA de 13 semanas (go-live 15/nov) eleva a coordenação de caminho crítico.</t>
+          <t>Dono da arquitetura; cobre solution + funcional de alto nível. Com a Arquitetura MESCLADA ao Planning &amp; Design da Fundação (ADR 0006), o SA fecha a arquitetura NA SEM. 1. Residência híbrida (ADR 0001) + instância dedicada greenfield (ADR 0002) + MuleSoft on-premise REUSADO (ADR 0006) governam o data model e a topologia de E01/E02/E03/E08 — coverage sênior contínuo por todo o build (S1-S13), amplificado por agentes.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -11578,12 +11795,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11608,7 +11825,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11619,7 +11836,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Dono da arquitetura; cobre solution + funcional de alto nível no MVP. Residência híbrida (ADR 0001) + instância dedicada/apartada (ADR 0002) governam o data model e a topologia de E01/E02/E03/E08 — coverage sênior contínuo, amplificado por agentes.</t>
+          <t>Risco #1: hub de integração E05 sem contratos de API, mock-first, com o gateway PCI como alvo (ADR 0003). Agora sobre MuleSoft on-premise REUSADO (ADR 0006) — sem lead-time de provisionamento, o TA arranca a frente de integração na Sem. 1. Sênior no caminho crítico dirigindo o fleet de agentes por todo o build; onshore por acoplamento de timezone com Dataprev/facilitadoras.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -11631,7 +11848,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11661,18 +11878,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>full-then-fractional</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1: full; 2: quarter; 3: quarter</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Risco #1: hub de integração E05 sem contratos de API, mock-first, agora com o gateway PCI como alvo (ADR 0003). Sênior no caminho crítico dirigindo o fleet de agentes; onshore por acoplamento de timezone com Dataprev/facilitadoras.</t>
+          <t>NOVO — arquiteto técnico dedicado à FRENTE MULESOFT contínua (E05), que se estende por todo o P&amp;D e DEV (S1-S11). Reuso da instalação on-premise existente (ADR 0006) não elimina o desenho da camada API-led: contratos, roteamento, de-tokenização em runtime, agendamento de conciliação por lotes e a integração do gateway PCI seguem no caminho crítico. Alocação INTEGRAL nas 4 primeiras semanas (arquitetura + P&amp;D da camada de integração, Sem. 1-4 = 160h) e 20h/sem nas semanas de DEV (Sem. 5-11 = 140h). Onshore pela soberania on-premise e acoplamento de timezone.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -11714,22 +11935,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>half-then-full</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3: full</t>
+          <t>1: half; 3: full</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOVO — E03 subiu de L para XL (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT — calcula/aplica o rateio (governo/facilitadora/estabelecimento) com teto de MDR 3,6% e repasse ≤15 dias (Decreto 12.712/2025), emite boletagem com o split aplicado e concilia por casamento. Especialista de arquitetura financeira/bancária: define as regras de split e conciliação (G0304, blocker de Fase 0/1) e o contrato de integração com o gateway PCI/banco custódia (G0309), e conduz o build de E03. Onshore por acoplamento regulatório e de timezone. Half nas fases 0-1 (arquitetura), full na Fase 3 (build de E03).</t>
+          <t>E03 é XL (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT — calcula/aplica o rateio (governo/facilitadora/estabelecimento) com teto de MDR 3,6% e repasse ≤15 dias (Decreto 12.712/2025), emite boletagem com o split aplicado e concilia por casamento. Especialista de arquitetura financeira/bancária: define as regras de split e conciliação (G0304) e o contrato de integração com o gateway PCI/banco custódia (G0309) na Fundação (half, Sem. 1-4 = 80h) e conduz o build da frente Financeiro em paralelo ao Marketplace (full, Sem. 6-11 = 240h). Onshore por acoplamento regulatório e de timezone.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -11751,7 +11972,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11782,7 +12003,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Coordenação multi-fase, release management, cadência com stakeholders. Ramp na Fase 1.</t>
+          <t>Accountability única de entrega e da relação MTE×Dataprev + coordenação multi-frente, release management e cadência com stakeholders. Senior PM full por todo o build (S1-S13) — o modelo AI-native e a data FIXA de 15/nov elevam a coordenação de caminho crítico e a governança das frentes paralelas (Marketplace + Financeiro correndo juntas). Absorve a accountability antes coberta por um Engagement Manager separado.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -11835,7 +12056,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AI-native — volume→agentes (adj.1): pod de 3→2 sob a arquitetura sênior; os builders remanescentes constroem COM agentes o leilão custom (E02, XL) e o motor de split (E03, XL), caminho crítico e alto imposto de review.</t>
+          <t>AI-native — volume→agentes (adj.1): pod de 3→2 sob a arquitetura sênior; os builders remanescentes constroem COM agentes o leilão custom (E02, XL) e o motor de split (E03, XL). Com o build re-derivado nas janelas mais longas (Marketplace 6 sem + Financeiro 6 sem em paralelo), os devs cobrem full por todo o programa (S1-S13 = 13 sem × 40h × 2 = 1.040h) — menor intensidade semanal por frente, maior prazo, menor risco.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -11888,7 +12109,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AI-native — volume→agentes (adj.1): 2→1. Stub/mock-first de E05 favorável a agentes; builder humano cobre a virada mock→real, a integração do gateway PCI (ADR 0003) e a de-tokenização em runtime (fora da fronteira do agente).</t>
+          <t>Frente MuleSoft CONTÍNUA (E05) por todo o P&amp;D e DEV (S1-S11 = 11 sem × 40h = 440h). Reuso da instalação on-premise existente (ADR 0006) favorece o arranque na Sem. 1; builder humano cobre a virada mock→real, a integração do gateway PCI (ADR 0003), a de-tokenização em runtime e o agendamento de conciliação por lotes (fora da fronteira do agente), sob o Arquiteto Técnico MuleSoft (R13).</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -11941,7 +12162,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Especialista fracional consumido (adj.5): jornada única gov.br (E01) + UX do leilão/comparação de propostas (E02); risco de adoção material.</t>
+          <t>Especialista fracional consumido (adj.5): jornada única gov.br (E01, na Fundação) + UX do leilão/comparação de propostas (E02, na frente Marketplace). Ativo da Sem. 1 à Sem. 8 (Fundação + primeira metade da frente Marketplace, onde o UX é definido) = 8 sem × 40h = 320h; risco de adoção material.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -11994,7 +12215,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AI-native — QA amplificado, NÃO reduzido (adj.2): agente não é check independente da própria saída. Mantido em 2 com surge no hardening — go-live financeiro regulado (idempotência/conciliação boleto/Pix/split, teto MDR 3,6%) numa data FIXA exige verificação humana. Janela de estabilização mínima (1 sem) pressiona o QA.</t>
+          <t>AI-native — QA amplificado, NÃO reduzido (adj.2): agente não é check independente da própria saída. Com o UAT ANTECIPADO (Sem. 8) e estendido a 6 semanas (Sem. 8-13, +1 sem vs. plano anterior), o QA acompanha as frentes em teste contínuo da Sem. 6 à Sem. 13 (8 sem × 40h × 2 = 640h) — go-live financeiro regulado (idempotência/conciliação boleto/Pix/split, teto MDR 3,6%) numa data FIXA exige verificação humana surge.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -12047,7 +12268,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>~800k estabelecimentos + ~450k beneficiárias (volumetria a ratificar); resistência à perda de margem no modelo transparente. Especialista fracional (um dia/semana).</t>
+          <t>~800k estabelecimentos + ~450k beneficiárias (volumetria a ratificar); resistência à perda de margem no modelo transparente. Especialista fracional (um dia/semana) da Sem. 1 à Sem. 13 (comms de mudança arrancam na Fundação, pico na adoção pré-go-live) = 13 sem × 20h = 260h.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -12100,7 +12321,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Carga inicial MÍNIMA de cadastros (E07, M) — Novo PAT permanece system-of-record; carga massiva pós-go-live. Fracional na Fase 4.</t>
+          <t>Carga inicial MÍNIMA de cadastros (E07, M) — Novo PAT permanece system-of-record; carga massiva pós-go-live. Agora em 2 SEMANAS (Sem. 12-13, as duas últimas — não apenas 1), fracional = 2 sem × 20h = 40h.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -12112,16 +12333,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Product Owner / Decisor</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>offshore</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>1</t>
@@ -12129,23 +12358,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>ps</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>half</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Decisor empoderado para destravar blockers (fronteira de residência com Jair Bogo, provisionamento da org dedicada, seleção do gateway PCI, regras do leilão/Lei 14.133), com a cadência que o modelo AI-native exige e a data FIXA impõe. ⚠ Não confirmado — gap de prontidão do cliente; é exatamente o que o gate AI-native testa.</t>
+          <t>SCALE/HYPERCARE — meio Consultor Técnico (0,5 FTE = 20h/sem × 4 sem = 80h). Responsabilidades: SUSTENTAR (triar/corrigir incidentes de estabilização) e MANTER a plataforma em produção. Sem build de nova funcionalidade.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -12157,16 +12386,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SMEs por épica</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>offshore</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>1</t>
@@ -12174,23 +12411,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>ps</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>full</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Conhecimento de Novo PAT, eSocial, folha, regras Lei 14.133 — disponível no momento (modelo native).</t>
+          <t>SCALE/HYPERCARE — 1 Dev MuleSoft INTEGRAL (1,0 FTE = 40h/sem × 4 sem = 160h). Reforçado de 0,5→1,0 FTE no grill 03/ago (APOSTA B): os primeiros ciclos reais folha→boleto→split→conciliação sob dinheiro real são o pico de incidência numa plataforma financeira regulada — meio-período não cobre um defeito de split/conciliação sob carga. Responsabilidades: MANTER a saúde das rotas MuleSoft on-premise e a conciliação/split em produção; apoiar o CUTOVER das integrações. Sem build de nova funcionalidade.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -12202,16 +12439,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Steward</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Technical Architect</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>senior</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>onshore</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>1</t>
@@ -12219,23 +12464,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>ps</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>fractional</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Origem e qualidade dos cadastros para E07 (Migração &amp; Carga).</t>
+          <t>SCALE/HYPERCARE — 10h/sem de Arquiteto Técnico × 4 sem = 40h. Responsabilidades: sustentar decisões de arquitetura em produção e conduzir o CUTOVER (virada operacional completa e handover à operação Dataprev).</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -12247,16 +12492,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Client IT / Plataforma</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Project/Program Manager</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>senior</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>onshore</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>1</t>
@@ -12264,23 +12517,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>ps</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>fractional</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Contratos de API das facilitadoras, hospedagem MuleSoft × residência, ponto de tokenização, provisionamento da instância dedicada (ADR 0002), contratação do gateway PCI (ADR 0003). Sub-staff aqui é o matador de entrega clássico e o maior risco à data fixa.</t>
+          <t>SCALE/HYPERCARE — 10h/sem de Senior PM × 4 sem = 40h. Responsabilidades: coordenar a sustentação, a manutenção e o CUTOVER; governar o handover à operação Dataprev ao fim da Sem. 17 (13/dez).</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -12292,12 +12545,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capacidade de UAT</t>
+          <t>Product Owner / Decisor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -12314,18 +12567,18 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>full</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Homologação do fluxo financeiro regulado (set/2026) antes de produção em 15/nov.</t>
+          <t>Decisor empoderado para destravar blockers (fronteira de residência com Jair Bogo, provisionamento da org dedicada, seleção do gateway PCI, regras do leilão/Lei 14.133), com a cadência que o modelo AI-native exige e a data FIXA impõe. Com o MuleSoft agora em reuso (ADR 0006), o provisionamento da org e a contratação do gateway correm em paralelo à Fundação (day-1) e são a decisão de cliente mais sensível. ⚠ Não confirmado — gap de prontidão do cliente.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -12337,12 +12590,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sponsor executivo</t>
+          <t>SMEs por épica</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -12359,18 +12612,18 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>quarter</t>
+          <t>half</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Alinhamento MTE × Dataprev; ratificação por escrito da instância dedicada (ADR 0002); monitorar ADI 7962/STF sobre o Decreto 12.712/2025.</t>
+          <t>Conhecimento de Novo PAT, eSocial, folha, regras Lei 14.133 — disponível no momento (modelo native).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -12378,6 +12631,186 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data Steward</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Origem e qualidade dos cadastros para E07 (Migração &amp; Carga Mínima), nas 2 semanas de carga (Sem. 12-13).</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Client IT / Plataforma</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ACESSO à instalação MuleSoft on-premise existente (reuso — ADR 0006), contratos de API das facilitadoras, ponto de tokenização, provisionamento da instância dedicada greenfield (ADR 0002), contratação do gateway PCI (ADR 0003). Sub-staff aqui é o matador de entrega clássico e o maior risco à data fixa remanescente após o reuso do MuleSoft.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capacidade de UAT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Homologação CONTÍNUA a partir da entrega do Marketplace (Sem. 8) até o go-live (Sem. 13) — janela de 6 semanas exige capacidade de UAT do cliente engajada mais cedo e por mais tempo que no plano anterior. Homologa marketplace, credenciamento e o fluxo financeiro regulado antes de produção em 15/nov.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sponsor executivo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Alinhamento MTE × Dataprev; ratificação por escrito da instância dedicada (ADR 0002) e do reuso do MuleSoft on-premise (ADR 0006); monitorar ADI 7962/STF sobre o Decreto 12.712/2025. Presente também no Scale/Hypercare (Etapa 5) para o cutover.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12545,7 +12978,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Data-alvo agressiva (homologação set/2026, produção 15/nov, ~15-16 sem abaixo do piso de 18) sinaliza viés de velocidade; MAS camadas de aprovação gov, incerteza jurídica (ADI no STF) e os blockers da Fase 0 temperam. Misto.</t>
+          <t>Data-alvo agressiva (homologação set/2026, produção 15/nov, ~15-16 sem abaixo do piso de 18) sinaliza viés de velocidade; MAS camadas de aprovação gov, incerteza jurídica (ADI no STF) e os blockers da Etapa 0 temperam. Misto.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -12661,7 +13094,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ambientes/dados de teste representativos prontos cedo; Contratos de API resolvidos na Fase 0 (reduz o mock-then-rework)</t>
+          <t>Ambientes/dados de teste representativos prontos cedo; Contratos de API resolvidos na Etapa 0 (reduz o mock-then-rework)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -12849,7 +13282,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A categoria de menor ganho. A IA sumariza status e recupera informação, mas o núcleo — alinhamento entre MTE × Dataprev × 600-700 facilitadoras, resolução dos blockers da Fase 0, coordenação da virada mock→real de E05 — é trabalho humano que não se move.</t>
+          <t>A categoria de menor ganho. A IA sumariza status e recupera informação, mas o núcleo — alinhamento entre MTE × Dataprev × 600-700 facilitadoras, resolução dos blockers da Etapa 0, coordenação da virada mock→real de E05 — é trabalho humano que não se move.</t>
         </is>
       </c>
     </row>
@@ -13020,341 +13453,3660 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Rate Basis</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Epic ID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>Phase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Validated By</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Validated At</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Indicative Low</t>
+          <t>Outcome Summary</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Indicative High</t>
+          <t>Has Metric</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Duration Weeks Range</t>
+          <t>Open Question Count</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Effort Basis</t>
+          <t>Build Target Present</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Disclaimer Class</t>
+          <t>Internal Dep Count</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>External Dep Count</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Requirement Count</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Artifact Count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quantum-leap</t>
+          <t>INT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>per-resource-hourly</t>
+          <t>Contract-first mock harness for external systems (mock→real governance)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Engagement Manager / Sr Solution Architect / Sr Technical Architect (onshore-senior)</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>884.68</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>Every external system the Novo PAT marketplace depends on is reachable through a versioned, contract-first mock behind a stable System API, so build proceeds before any real Swagger exists and swaps to the real endpoint without rework.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11 linhas PS: 4 sênior onshore (EM, SA, TA, Payments TA) + 1 PM regular onshore + 3 Devs regular offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional). Roster comprometido da trilha AI-native (resource-plan.json).</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>input-derived</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quantum-leap</t>
+          <t>INT-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>per-resource-hourly</t>
+          <t>CPF de-tokenization / identity-resolution service on-premise</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Project Manager / Experience Architect (onshore-regular &amp; offshore-regular design)</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>789.88</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>The Salesforce core references workers and establishments by non-sensitive token; nominal/CPF data is resolved at runtime, only when authorized, inside the Dataprev sovereign perimeter and never persisted in the Salesforce cloud.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11 linhas PS: 4 sênior onshore (EM, SA, TA, Payments TA) + 1 PM regular onshore + 3 Devs regular offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional). Roster comprometido da trilha AI-native (resource-plan.json).</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>input-derived</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quantum-leap</t>
+          <t>INT-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>per-resource-hourly</t>
+          <t>External-caller authentication &amp; rate-limited token validation gateway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Developer / Technical Consultant / MuleSoft TC (offshore-regular)</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>668.78</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>security</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>External callers (facilitadoras, adquirente) authenticate by CNPJ via client-credentials flow against a scope-restricted connected app; tokens are validated with rate limiting and caching before any integration endpoint runs.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11 linhas PS: 4 sênior onshore (EM, SA, TA, Payments TA) + 1 PM regular onshore + 3 Devs regular offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional). Roster comprometido da trilha AI-native (resource-plan.json).</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>input-derived</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quantum-leap</t>
+          <t>INT-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>per-resource-hourly</t>
+          <t>Federal-source read &amp; validation System APIs (mock-first)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quality Assurance Consultant / Solution Consultant (offshore &amp; onshore-regular advisory)</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>573.98</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>Assumed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>The platform validates a beneficiária's/facilitadora's regular standing and reads required reference data from federal sources (Novo PAT regularity, GOV.BR/Geride, eSocial, SDC) through System APIs, running on mocks now and cutting over to real endpoints when contracts land.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3740984</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11 linhas PS: 4 sênior onshore (EM, SA, TA, Payments TA) + 1 PM regular onshore + 3 Devs regular offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional). Roster comprometido da trilha AI-native (resource-plan.json).</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>input-derived</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INT-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INIS PJ / Kinis PJ termo-de-aceite data ingest</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The platform ingests the acceptance-term data originated in INIS PJ/Kinis PJ — worker counts by salary band and matriz/filial structure — as the source of the beneficiária's termo de aceite, referenced by non-sensitive identifier in the core.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INT-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Facilitadora standard contract: Quote hand-off, processed-return, open-demand pull endpoint</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Every one of the ~600–700 facilitadoras integrates through one standard API contract: it receives Quotes, returns the processed result plus value, and can pull the open demands in the current vigência — a certifiable single contract, not a bespoke connector per facilitadora.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INT-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adquirente credenciamento-check API &amp; transaction-monitoring ingest</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>An adquirente can query an establishment's accreditation status before processing a transaction, and sends all transactions into the platform for monitoring — the a-posteriori visibility feed for the MTE.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INT-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Scheduled incremental bank-movement reconciliation feed (gateway → CRM)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>On a MuleSoft schedule, the platform pulls the registered boleto and the incremental bank movements returned by the gateway/banco custódia and lands them in the CRM so the split boletagem can be matched to what was actually paid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INT-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Modelo de dados de referências tokenizadas — CPF e dados sensíveis nunca persistem na org</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Os objetos do PAT (cotação, proposta, contrato, folha, beneficiária, estabelecimento) referenciam pessoas e estabelecimentos por um identificador não-sensível; nenhum CPF ou dado pessoal sensível é gravado em campo, anexo, histórico ou log da org Salesforce.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INT-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Contrato de de-tokenização em runtime via MuleSoft on-premise</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Quando um usuário autorizado precisa ver o dado nominal de uma beneficiária/estabelecimento, a org resolve o identificador tokenizado em runtime por uma chamada ao MuleSoft on-premise, que de-tokeniza no perímetro soberano Dataprev — sem que o dado resolvido seja gravado na org.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INT-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trilha de auditoria imutável de acesso a dado sensível</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Todo acesso a dado sensível (resolução de identificador, leitura de campo-fronteira, ação sobre registro financeiro) gera um registro de trilha imutável — quem, o quê, quando — que sustenta escrutínio de TCU/CGU/ANPD e não pode ser alterado nem apagado por administrador.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INT-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mascaramento de CPF em logs, depuração e mensagens de erro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CPF e dados pessoais sensíveis nunca aparecem em claro em logs de sistema, logs de depuração, mensagens de erro, notificações ou telas de diagnóstico — são mascarados ou substituídos pela referência tokenizada em toda saída observável.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>INT-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Modelo de isolamento e acesso de menor privilégio na org dedicada</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Dentro da instância dedicada e apartada do MTE/PAT, o acesso a dado sensível e a operações financeiras é concedido por menor privilégio via permission sets e modelo de compartilhamento, de modo que só perfis autorizados resolvem dado nominal e nenhum administrador de outro ambiente Dataprev enxerga estes dados.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INT-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Autenticação gov.br via OpenID Connect no Experience Cloud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uma representante de uma empresa beneficiária entra no portal do PAT usando sua conta gov.br, sem senha própria da plataforma — a identidade gov.br é a única porta de entrada.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INT-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Seleção 'representar empresa' dirigida por procuração</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Após o login, a representante vê apenas os CNPJs que sua procuração digital a autoriza a operar, escolhe uma empresa (Matriz ou Filial) e passa a navegar o portal naquele contexto — podendo trocar de empresa pelo menu superior.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INT-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Validação de vínculo CPF↔CNPJ via Geride</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A lista de empresas que a representante pode operar reflete os vínculos válidos e ativos apurados na fonte oficial em tempo de acesso — vínculo revogado ou empresa irregular não aparece nem é operável.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INT-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Controle de acesso e navegação do portal por papel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Cada tipo de usuário vê e opera somente o que seu papel permite — a representante da beneficiária navega cotação/folha da(s) empresa(s) que representa; o estabelecimento vê seu próprio escopo; o administrador do MTE tem sua visão de gestão — sem cruzar dados entre empresas.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INT-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sessão e logout federado gov.br</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A sessão do portal tem começo e fim claros: ao sair, a representante encerra a sessão do Experience Cloud e o vínculo com a identidade gov.br, sem deixar contexto de empresa aberto para um próximo acesso indevido.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INT-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Publicação da demanda como Opportunity nativa (leilão reverso)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A beneficiária registra sua demanda de leilão reverso como uma Opportunity nativa do Sales Cloud, com todos os parâmetros que as facilitadoras precisam para cotar.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INT-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Recepção de Quotes das facilitadoras via API dentro da vigência</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N facilitadoras submetem propostas como Quotes nativas associadas à Opportunity aberta, exclusivamente via API, sem UI nem licença de portal — a equidade é por construção.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>INT-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Máquina de estados da janela de vigência + trava de seleção até o fechamento</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O ciclo da demanda transita por estados regidos pela janela de vigência; a beneficiária vê as Quotes conforme chegam, mas a seleção fica travada até a janela fechar (não é seleção cega).</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>INT-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tela Comparar Propostas (LWC) lado a lado</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>lwc</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A beneficiária compara as Quotes recebidas lado a lado numa tela custom, com os atributos decisórios normalizados para comparação justa.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>INT-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Seleção do vencedor → firmamento do contrato</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>screen-flow</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Após o fechamento da janela, a beneficiária seleciona uma Quote e a plataforma transita a demanda para contrato firmado, com trilha de justificativa.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>INT-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Upload e versionamento do PDF de contrato (sem CLM)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A facilitadora anexa o PDF imutável do contrato com metadados e versões (aditivo = nova versão), sem gestão de ciclo de vida de contrato.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>INT-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Termo de aceite: classificação por faixa salarial + matriz/filial → Novo PAT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>screen-flow</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Após o contrato firmado, a beneficiária classifica o nº de trabalhadores acima/abaixo de 5 salários mínimos por CNPJ e matriz/filial, e o aceite é integrado ao Novo PAT via INIS PJ.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>INT-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ramificação de regras de cálculo PAT vs. não-PAT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Beneficiárias PAT e não-PAT contratam pela mesma plataforma, mas com regras de cálculo distintas — PAT sob o teto de 3,6%, não-PAT sem benefício fiscal.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INT-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carga de contratos legados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Contratos legados existentes são carregados na plataforma, mapeados à estrutura nativa Opportunity/Quote/Account com seus PDFs e metadados.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INT-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Autocadastro de estabelecimento via gov.br (PJ)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Um estabelecimento se cadastra uma única vez no portal, autenticado como PJ via gov.br, e a plataforma cria um registro pendente na base nacional unificada de estabelecimentos — substituindo o credenciamento repetido facilitadora a facilitadora.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Envio de documentos do estabelecimento com checklist guiado</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O estabelecimento sobe os documentos exigidos para o credenciamento (licença sanitária, comprovações de regularidade) anexados ao seu registro, com orientação de quais documentos são necessários e por que o cadastro está pendente.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>INT-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Validação documental automatizada com transbordo humano</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>A plataforma aplica regras determinísticas de validação sobre o cadastro e os documentos (CNPJ ativo, CNAE compatível com alimentação, integridade do documento) e resolve automaticamente os casos claros, transbordando para análise humana somente as exceções.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Análise documento a documento e parecer do Analista MTE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>console</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Um Analista MTE analisa cada documento do estabelecimento (Válido/Inválido + motivo), emite um parecer sobre o credenciamento (Deferido / Exigência complementar / Indeferido) e toda a operação fica registrada em trilha de auditoria.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>INT-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ação legal de aprovar e descredenciar (facilitadora/MTE) com propagação de status</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>console</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>A facilitadora mantém o papel legal de aprovar e descredenciar o estabelecimento na sua relação, e o MTE pode descredenciar do programa; a mudança de status vira o estado consultável pela base de estabelecimentos que o adquirente lê antes de transacionar.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>INT-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Captura da licença sanitária com extração de campos por IA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>A plataforma captura a data de validade da licença sanitária — o único campo comum aos 5000+ padrões municipais sem base unificada — usando extração por IA sobre o documento enviado, com o analista confirmando o valor quando a extração não for confiável.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>INT-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rastreio de vencimento, renovação e alertas de expiração</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>A plataforma rastreia a data de validade da licença de cada estabelecimento, dispara alertas com antecedência antes do vencimento e conduz o fluxo de renovação, de modo que uma licença não expire silenciosamente e o estabelecimento continue apto.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INT-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recepção assíncrona de folha (upload CSV via portal/API, desacoplado)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>A beneficiária envia o CSV da folha da competência pelo portal ou por API e recebe confirmação de recebimento em segundos; o arquivo entra numa fila de processamento sem travar a sessão nem consumir um slot de processamento longo.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INT-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Validação de layout e integridade da folha (não quebrada)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Toda folha enfileirada passa por uma checagem automática de layout e integridade estrutural; folhas íntegras seguem para disponibilização à facilitadora e as inconsistentes são sinalizadas à beneficiária com o motivo, sem persistir as linhas.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INT-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Crítica da folha por IA (assíncrona; melhor alternativa Salesforce a definir)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Folhas que passam na validação estrutural recebem uma crítica automática mais rica (consistência dos dados da competência) executada de forma assíncrona; o resultado alimenta a liberação para download sem que a crítica rode no clique do upload.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INT-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Modelo de dados financeiro (folha cabeçalho/competência, contrato, regras de split)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>A plataforma tem os objetos custom que sustentam o ciclo financeiro — folha por competência (só cabeçalho), contrato/vigência e regras de split parametrizáveis — sobre a base Sales Cloud, sem Revenue Cloud e sem persistir linhas de folha.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INT-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Disponibilização da folha à facilitadora e retorno de 'processado + valor'</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>A facilitadora baixa a folha íntegra por contrato e vigência (mês-ano) via API e devolve à plataforma o status 'processado' com o valor a pagar, que passa a alimentar a emissão de boleto.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>INT-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Solicitação e recebimento de boleto registrado junto ao gateway</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Com o valor da folha processado, a plataforma envia a instrução de cobrança ao gateway (que intermedia a conta custódia) e recebe de volta o boleto registrado com metadados e link, sem movimentar dinheiro.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>INT-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Disponibilização do boleto à beneficiária no portal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>experience-cloud</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Assim que o boleto registrado retorna do gateway, a beneficiária o encontra disponível no portal (link/metadados) vinculado à folha da competência.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>INT-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Conciliação agendada de movimentações bancárias (casamento incremental) e identificação de pagamento</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>A plataforma recebe do gateway as movimentações bancárias em lotes incrementais por agendamento e faz o casamento com os boletos emitidos, identificando o pagamento e avançando o status da folha automaticamente.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>INT-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Motor de regras de split (teto MDR 3,6%, repasse ≤15 dias, ramificação PAT vs não-PAT)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Identificado o pagamento, a plataforma consulta as regras de split e calcula o rateio entre facilitadora, governo/MTE e demais partes, aplicando o teto de MDR de 3,6%, a distinção entre beneficiária PAT e não-PAT e o prazo de repasse de até 15 dias.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>INT-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Registro do racional de cálculo (trilha auditável) e entrega das ordens de transferência ao gateway</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>A plataforma registra todo o racional do repasse — datas, split aplicado, ordens de transferência — como trilha auditável e entrega as ordens de transferência ao gateway via MuleSoft, que executa a movimentação.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>INT-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Status consolidado 'crédito concedido' e gatilho de notificação (empresa + CTPS Digital)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Concluído o repasse, a folha exibe um status consolidado 'crédito concedido' em uma única linha (não por trabalhador) e dispara a notificação à empresa e, via CTPS Digital, a 'expectativa de crédito' ao trabalhador — monitoramento apenas na Fase 1.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>INT-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Carga inicial idempotente de referências não-sensíveis (Bulk API 2.0 + upsert por external ID)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>O conjunto mínimo de beneficiárias, facilitadoras e estabelecimentos necessário ao go-live de 15/nov entra no Salesforce como referências tokenizadas não-sensíveis, sem CPF nem dado nominal persistido, por uma carga re-executável que não duplica registros ao rodar de novo.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deduplicação na carga por chave não-sensível</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>data-model</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Registros duplicados de estabelecimentos e beneficiárias não entram como referências redundantes: a carga reconhece o mesmo CNPJ (ou CNPJ+UF) vindo de fontes diferentes e colapsa em uma única referência tokenizada.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>INT-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Validação de qualidade e reconciliação pós-carga</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Assumed</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ao fim da carga há prova de que ela bateu com a fonte-de-verdade e de que nenhum dado sensível foi persistido, com critério de aceite e reprocessamento idempotente em caso de falha parcial — condição para defender a carga em auditoria.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>INT-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Painel de adoção do portal da beneficiária</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>lightning-record-page</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Um patrocinador do programa (MTE/Dataprev) enxerga, num painel, o quanto as beneficiárias estão de fato usando o portal e progredindo no funil de cotação — logins, necessidades publicadas, propostas recebidas, seleções e contratos — para dirigir o esforço de adoção onde ele trava.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13369,7 +17121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13380,57 +17132,62 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Anchor</t>
+          <t>Rate Basis</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Validated By</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Validated At</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Indicative Low</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Indicative High</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Duration Weeks Range</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Indicative Price Low</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Indicative Price High</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Roster</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Capacity Summary</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Delta vs Other Lane</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Validated By</t>
+          <t>Effort Basis</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
           <t>Disclaimer Class</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -13442,91 +17199,263 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>per-resource-hourly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sr Solution Architect / Sr Technical Architect / MuleSoft Technical Architect / Payments Architecture Specialist / Senior Project Manager (onshore-senior)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>884.68</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'low': 11, 'high': 27}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1x Project/Program Manager (senior onshore); 1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (regular onshore); 2x Developer (regular offshore); 1x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore); 1x Product Owner / Decisor; 1x SMEs por épica; 1x Data Steward; 1x Client IT / Plataforma; 1x Capacidade de UAT; 1x Sponsor executivo</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{'program_avg_fte': 8.9, 'peak_distinct_people': 12, 'ps_person_hours': 4620, 'blended_rate_no_tax': 756.7, 'note': 'FTE média-programa = 4620 PS person-hours / (13 sem × 40). Roster comprometido: financeiro/bancário adicionado (E03 XL), Agentforce E06 removido do MVP (de-escopo). Pico maior no meio do build.'}</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>A comparação agora tem duas camadas. (1) COMPROMETIDO: MVP AI-native na janela FIXA de 13 semanas = ponto indicativo de R$ 3,50M sem imposto / R$ 3,74M com imposto (~8,9 FTE média-programa). (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>input-derived</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>traditional</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>quantum-leap</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>per-resource-hourly</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Project Manager / Experience Architect (onshore-regular &amp; offshore-regular design)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'low': 18, 'high': 38}</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>789.88</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1x Project/Program Manager (senior onshore); 1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (regular onshore); 3x Developer (regular offshore); 2x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Developer (senior offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore)</t>
+          <t>4184469</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'program_avg_fte': 10.6, 'peak_distinct_people': 16, 'person_hours_range': {'low': 7420, 'high': 15670}, 'blended_rate_no_tax': 736.0, 'note': 'Pod de build offshore que escala com volume + oversight sênior onshore + especialista financeiro/bancário (E03 XL). Escopo completo (9 épicas, inclui E06).'}</t>
+          <t>4184469</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A comparação agora tem duas camadas. (1) COMPROMETIDO: MVP AI-native na janela FIXA de 13 semanas = ponto indicativo de R$ 3,50M sem imposto / R$ 3,74M com imposto (~8,9 FTE média-programa). (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
+          <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>quantum-leap</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>per-resource-hourly</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Developer / Technical Consultant / MuleSoft TC (offshore-regular)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>668.78</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>input-derived</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>quantum-leap</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>per-resource-hourly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality Assurance Consultant / Solution Consultant (offshore &amp; onshore-regular advisory)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>573.98</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4184469</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/Scopezilla/DATAPREV-PAT/outputs/scoping-deliverables.xlsx
+++ b/Scopezilla/DATAPREV-PAT/outputs/scoping-deliverables.xlsx
@@ -785,17 +785,17 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (senior onshore); 2x Developer (regular offshore); 1x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore); 1x Developer (Scale) (regular offshore); 1x Developer (Scale) (regular offshore); 1x Technical Architect (Scale) (senior onshore); 1x Project/Program Manager (Scale) (senior onshore); 1x Product Owner / Decisor; 1x SMEs por épica; 1x Data Steward; 1x Client IT / Plataforma; 1x Capacidade de UAT; 1x Sponsor executivo</t>
+          <t>1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Developer (regular onshore); 1x Project/Program Manager (senior onshore); 2x Developer (regular offshore); 1x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore); 1x Developer (Scale) (regular offshore); 1x Developer (Scale) (regular offshore); 1x Technical Architect (Scale) (senior onshore); 1x Project/Program Manager (Scale) (senior onshore); 1x Product Owner / Decisor; 1x SMEs por épica; 1x Data Steward; 1x Client IT / Plataforma; 1x Capacidade de UAT; 1x Sponsor executivo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'program_avg_fte': 9.4, 'peak_distinct_people': 13, 'ps_person_hours': 5200, 'ps_person_hours_build': 4880, 'ps_person_hours_scale': 320, 'blended_rate_no_tax': 754.0, 'note': 'FTE média do build = 4.880 PS person-hours / (13 sem × 40) = 9,4. Roster re-derivado por janela no plano paralelizado: Arquiteto Técnico MuleSoft sênior ADICIONADO (frente E05 contínua S1-S11), Senior PM absorve a accountability antes do Engagement Manager (removido), devs full por todo o build (janelas longas). + 4 semanas de Scale/Hypercare (320h, reusa perfis do build; Dev MuleSoft reforçado 0,5→1,0 FTE no grill 03/ago). Pico de 13 pessoas no meio do build.'}</t>
+          <t>{'program_avg_fte': 9.4, 'peak_distinct_people': 13, 'ps_person_hours': 5200, 'ps_person_hours_build': 4880, 'ps_person_hours_scale': 320, 'blended_rate_no_tax': 735.9, 'note': 'FTE média do build = 4.880 PS person-hours / (13 sem × 40) = 9,4. Roster re-derivado por janela no plano paralelizado: Arquiteto Técnico MuleSoft (frente E05 contínua S1-S11, rate 821,49), Senior PM absorve a accountability antes do Engagement Manager (removido), devs full por todo o build (janelas longas). + 4 semanas de Scale/Hypercare (320h, reusa perfis do build; Consultor Técnico 1,0 FTE integral + 0,5 Dev MuleSoft, corrigido 03/ago). Blended de build = R$ 3.591.059,40 / 4.880h = 735,9. Pico de 13 pessoas no meio do build.'}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,91M sem imposto / R$ 4,18M com imposto (~9,4 FTE média no build). Build R$ 3,68M sem imposto; Scale R$ 0,23M sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
+          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,82M sem imposto / R$ 4,09M com imposto (~9,4 FTE média no build). Build R$ 3,59M sem imposto; Scale R$ 0,23M sem imposto. Rates corrigidos em 03/ago (MuleSoft TA 821,49; ex-Payments→Technical Consultant 668,78) reduziram o total em R$ 88.045 sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1x Project/Program Manager (senior onshore); 1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Project/Program Manager (regular onshore); 3x Developer (regular offshore); 2x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Developer (senior offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore)</t>
+          <t>1x Project/Program Manager (senior onshore); 1x Solution Architect (senior onshore); 1x Technical Architect (senior onshore); 1x Developer (regular onshore); 1x Project/Program Manager (regular onshore); 3x Developer (regular offshore); 2x Developer (regular offshore); 1x Experience Design (regular offshore); 2x Quality Assurance (regular offshore); 1x Developer (senior offshore); 1x Change &amp; Adoption (regular onshore); 1x Developer (regular offshore)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,91M sem imposto / R$ 4,18M com imposto (~9,4 FTE média no build). Build R$ 3,68M sem imposto; Scale R$ 0,23M sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
+          <t>A comparação tem duas camadas. (1) COMPROMETIDO: Fase 1 AI-native = 13 semanas de build (17/ago-14/nov) + 4 semanas de Scale/Hypercare (16/nov-13/dez) = ponto indicativo de R$ 3,82M sem imposto / R$ 4,09M com imposto (~9,4 FTE média no build). Build R$ 3,59M sem imposto; Scale R$ 0,23M sem imposto. Rates corrigidos em 03/ago (MuleSoft TA 821,49; ex-Payments→Technical Consultant 668,78) reduziram o total em R$ 88.045 sem imposto. (2) NOTIONAL: o escopo completo pelo jeito tradicional custaria ~R$ 5,8-12,3M com imposto E não alcançaria 15/nov. O delta portanto não é só de custo — é de VIABILIDADE: a trilha tradicional está fora da data.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E05 corre como frente MuleSoft contínua (S1-S11) com UM builder humano (R06, Dev MuleSoft integral) + Arquiteto MuleSoft fracional (R13, 20h/sem no dev) + especialista de pagamentos (R12). Marketplace (S5-10) e Financeiro (S6-11) consomem integração EM PARALELO. O dimensionamento aposta que o lado Marketplace exige só um endpoint de consulta leve (pull, facilitadora API-only), concentrando a carga pesada de MuleSoft no Financeiro.</t>
+          <t>E05 corre como frente MuleSoft contínua (S1-S11) com UM builder humano (R06, Dev MuleSoft integral) + Arquiteto MuleSoft fracional (R13, 20h/sem no dev) + Consultor Técnico da frente Financeiro (R12, ex-Payments, rate corrigido 668,78 em 03/ago). Marketplace (S5-10) e Financeiro (S6-11) consomem integração EM PARALELO. O dimensionamento aposta que o lado Marketplace exige só um endpoint de consulta leve (pull, facilitadora API-only), concentrando a carga pesada de MuleSoft no Financeiro.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scale/Hypercare (S14-S17) cobre os primeiros 4 ciclos reais de produção com 0,5 Consultor Técnico (20h/sem) + 1 Dev MuleSoft integral (40h/sem) + 10h/sem Arquiteto Técnico + 10h/sem Senior PM. Alocação especificada pelo Solution Manager.</t>
+          <t>Scale/Hypercare (S14-S17) cobre os primeiros 4 ciclos reais de produção com 1,0 Consultor Técnico integral (40h/sem) + 0,5 Dev MuleSoft (20h/sem) + 10h/sem Arquiteto Técnico + 10h/sem Senior PM (mesmo arquiteto e mesmo PM do build). Alocação especificada pelo Solution Manager.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>✅ RESOLVIDO no grill 03/ago (APOSTA B). O watch de carga de incidentes foi aceito pelo usuário e mitigado na origem: o Dev MuleSoft do Scale foi reforçado de 0,5 FTE (20h/sem) para 1,0 FTE integral (40h/sem) nas 4 semanas — +80h → Scale 320h, total do programa 5.200h. Justificativa: os primeiros ciclos folha→boleto→split→conciliação sob dinheiro real são o pico de incidência numa plataforma financeira regulada, e um dev integral (não meio-período) cobre esse surge sem depender de acionamento reativo. Propagado a todos os outputs (resource-plan, commercials, estimate-comparison, roadmap, 02-delivery-plan, rom-cliente.html, deal-review.html, presentation-deck.html + PPTX).</t>
+          <t>✅ RESOLVIDO. Composição revista em 03/ago (supera a APOSTA B do grill de 03/ago): o esforço integral de sustentação nas 4 semanas passa a ser coberto pelo Consultor Técnico (0,5→1,0 FTE = 160h) e o Dev MuleSoft recua para meio-período (1,0→0,5 FTE = 80h). O total do Scale permanece 320h (troca compensada, ambos @ 668,78) e o total do programa segue 5.200h. Justificativa: sustentar/manter a plataforma sob dinheiro real é trabalho de período integral, e o Consultor Técnico é o perfil primário de estabilização; o Dev MuleSoft cobre meio-período as rotas on-premise + conciliação/split e apoia o cutover. Propagado a todos os outputs (resource-plan, commercials, estimate-comparison, 02-delivery-plan, rom-cliente.html, deal-review.html, presentation-deck.html + PPTX).</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Salesforce Developer, Payments/Financial Architecture Specialist (arquitetura bancária/split), MuleSoft Developer</t>
+          <t>Salesforce Developer, Technical Consultant (arquitetura bancária/split), MuleSoft Developer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4 semanas de Scale/Hypercare A PARTIR DE 16/nov/2026 (dia seguinte ao go-live), com uma equipe enxuta cujas responsabilidades são EXCLUSIVAMENTE: SUSTENTAR a operação em produção (monitorar, triar e corrigir incidentes de estabilização), MANTER a plataforma e as integrações on-premise (ajustes finos, saúde das rotas MuleSoft, conciliação/split em produção) e conduzir o CUTOVER (virada operacional completa, escalonamento da carga pós-mínima e handover à operação Dataprev). NÃO há build de nova funcionalidade no Scale — é janela de estabilização, não de escopo novo. Equipe: meio Consultor Técnico (0,5 FTE = 20h/sem), UM Dev MuleSoft integral (1,0 FTE = 40h/sem — reforçado de 0,5 para 1,0 no grill de 03/ago, dado o pico de incidência dos primeiros ciclos financeiros reais sob dinheiro real), 10h/sem de um Arquiteto Técnico e 10h/sem de um Senior PM, nas 4 semanas.</t>
+          <t>4 semanas de Scale/Hypercare A PARTIR DE 16/nov/2026 (dia seguinte ao go-live), com uma equipe enxuta cujas responsabilidades são EXCLUSIVAMENTE: SUSTENTAR a operação em produção (monitorar, triar e corrigir incidentes de estabilização), MANTER a plataforma e as integrações on-premise (ajustes finos, saúde das rotas MuleSoft, conciliação/split em produção) e conduzir o CUTOVER (virada operacional completa, escalonamento da carga pós-mínima e handover à operação Dataprev). NÃO há build de nova funcionalidade no Scale — é janela de estabilização, não de escopo novo. Equipe: UM Consultor Técnico integral (1,0 FTE = 40h/sem — reforçado de 0,5 para 1,0 em 03/ago, pois sustentar/manter a plataforma sob dinheiro real é trabalho de período integral), meio Dev MuleSoft (0,5 FTE = 20h/sem), 10h/sem de um Arquiteto Técnico e 10h/sem de um Senior PM (o mesmo arquiteto e o mesmo PM do build), nas 4 semanas.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -11910,12 +11910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E03 é XL (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT — calcula/aplica o rateio (governo/facilitadora/estabelecimento) com teto de MDR 3,6% e repasse ≤15 dias (Decreto 12.712/2025), emite boletagem com o split aplicado e concilia por casamento. Especialista de arquitetura financeira/bancária: define as regras de split e conciliação (G0304) e o contrato de integração com o gateway PCI/banco custódia (G0309) na Fundação (half, Sem. 1-4 = 80h) e conduz o build da frente Financeiro em paralelo ao Marketplace (full, Sem. 6-11 = 240h). Onshore por acoplamento regulatório e de timezone.</t>
+          <t>E03 é XL (ADR 0003): o Salesforce é o MOTOR DE REGRAS DE SPLIT — calcula/aplica o rateio (governo/facilitadora/estabelecimento) com teto de MDR 3,6% e repasse ≤15 dias (Decreto 12.712/2025), emite boletagem com o split aplicado e concilia por casamento. Consultor Técnico dedicado à frente Financeiro: implementa as regras de split e conciliação (G0304) e o contrato de integração com o gateway PCI/banco custódia (G0309) na Fundação (half, Sem. 1-4 = 80h) e conduz o build da frente Financeiro em paralelo ao Marketplace (full, Sem. 6-11 = 240h). Onshore por acoplamento regulatório e de timezone. Rate corrigido para Technical Consultant (R$ 668,78) em 03/ago — antes mapeado provisoriamente a Senior TA.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -12368,13 +12368,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>full</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SCALE/HYPERCARE — meio Consultor Técnico (0,5 FTE = 20h/sem × 4 sem = 80h). Responsabilidades: SUSTENTAR (triar/corrigir incidentes de estabilização) e MANTER a plataforma em produção. Sem build de nova funcionalidade.</t>
+          <t>SCALE/HYPERCARE — Consultor Técnico INTEGRAL (1,0 FTE = 40h/sem × 4 sem = 160h). Reforçado de 0,5→1,0 FTE em 03/ago: nas 4 semanas pós-go-live sob dinheiro real, sustentar e manter a plataforma (triar/corrigir incidentes de estabilização, ajustes de configuração) é trabalho de período integral. Responsabilidades: SUSTENTAR (triar/corrigir incidentes de estabilização) e MANTER a plataforma em produção. Sem build de nova funcionalidade.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -12421,13 +12421,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>half</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SCALE/HYPERCARE — 1 Dev MuleSoft INTEGRAL (1,0 FTE = 40h/sem × 4 sem = 160h). Reforçado de 0,5→1,0 FTE no grill 03/ago (APOSTA B): os primeiros ciclos reais folha→boleto→split→conciliação sob dinheiro real são o pico de incidência numa plataforma financeira regulada — meio-período não cobre um defeito de split/conciliação sob carga. Responsabilidades: MANTER a saúde das rotas MuleSoft on-premise e a conciliação/split em produção; apoiar o CUTOVER das integrações. Sem build de nova funcionalidade.</t>
+          <t>SCALE/HYPERCARE — meio Dev MuleSoft (0,5 FTE = 20h/sem × 4 sem = 80h). Ajustado de 1,0→0,5 FTE em 03/ago: o esforço integral de sustentação nas 4 semanas migra para o Consultor Técnico (S01); o Dev MuleSoft cobre meio-período para MANTER a saúde das rotas MuleSoft on-premise e a conciliação/split em produção e apoiar o CUTOVER das integrações. Sem build de nova funcionalidade.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -17121,7 +17121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sr Solution Architect / Sr Technical Architect / MuleSoft Technical Architect / Payments Architecture Specialist / Senior Project Manager (onshore-senior)</t>
+          <t>Sr Solution Architect / Sr Technical Architect / Senior Project Manager (onshore-senior)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 3 sênior onshore no tier 884,68 (SA, TA, Senior PM) + 1 Arquiteto Técnico MuleSoft no tier 821,49 + 1 Technical Consultant onshore na frente Financeiro (ex-Payments, 668,78) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 1,0 Consultor Técnico INTEGRAL + 0,5 Dev MuleSoft + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando os mesmos perfis do build (mesmo arquiteto e mesmo PM). SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Project Manager / Experience Architect (onshore-regular &amp; offshore-regular design)</t>
+          <t>MuleSoft Technical Architect (onshore-senior)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>789.88</t>
+          <t>821.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 3 sênior onshore no tier 884,68 (SA, TA, Senior PM) + 1 Arquiteto Técnico MuleSoft no tier 821,49 + 1 Technical Consultant onshore na frente Financeiro (ex-Payments, 668,78) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 1,0 Consultor Técnico INTEGRAL + 0,5 Dev MuleSoft + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando os mesmos perfis do build (mesmo arquiteto e mesmo PM). SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -17338,12 +17338,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Developer / Technical Consultant / MuleSoft TC (offshore-regular)</t>
+          <t>Project Manager / Experience Architect (onshore-regular &amp; offshore-regular design)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>668.78</t>
+          <t>789.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -17363,12 +17363,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4184469</t>
+          <t>4090253</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 3 sênior onshore no tier 884,68 (SA, TA, Senior PM) + 1 Arquiteto Técnico MuleSoft no tier 821,49 + 1 Technical Consultant onshore na frente Financeiro (ex-Payments, 668,78) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 1,0 Consultor Técnico INTEGRAL + 0,5 Dev MuleSoft + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando os mesmos perfis do build (mesmo arquiteto e mesmo PM). SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -17405,55 +17405,122 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Developer / Technical Consultant / MuleSoft TC (offshore-regular)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>668.78</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4090253</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4090253</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 3 sênior onshore no tier 884,68 (SA, TA, Senior PM) + 1 Arquiteto Técnico MuleSoft no tier 821,49 + 1 Technical Consultant onshore na frente Financeiro (ex-Payments, 668,78) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 1,0 Consultor Técnico INTEGRAL + 0,5 Dev MuleSoft + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando os mesmos perfis do build (mesmo arquiteto e mesmo PM). SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>input-derived</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>quantum-leap</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>per-resource-hourly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Quality Assurance Consultant / Solution Consultant (offshore &amp; onshore-regular advisory)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>573.98</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4184469</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4184469</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4090253</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4090253</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>17 (13 de build/Fase 1 + 4 de Scale/Hypercare)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 5 sênior onshore (SA, TA, Arquiteto Técnico MuleSoft NOVO, Payments TA, Senior PM) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 0,5 Consultor Técnico + 1,0 Dev MuleSoft INTEGRAL + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando perfis do build. SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>15 linhas PS: BUILD (11 linhas, 4.880h) = 3 sênior onshore no tier 884,68 (SA, TA, Senior PM) + 1 Arquiteto Técnico MuleSoft no tier 821,49 + 1 Technical Consultant onshore na frente Financeiro (ex-Payments, 668,78) + 2 Devs regular offshore + 1 MuleSoft TC offshore + 1 Experience Design offshore + 2 QA offshore + 1 Change &amp; Adoption onshore (fracional) + 1 Technical Consultant offshore (carga, fracional). SCALE/HYPERCARE (4 linhas, 320h) = 1,0 Consultor Técnico INTEGRAL + 0,5 Dev MuleSoft + 10h/sem Arquiteto Técnico + 10h/sem Senior PM, reusando os mesmos perfis do build (mesmo arquiteto e mesmo PM). SEM Engagement Manager separado (accountability absorvida pelo Senior PM full).</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>input-derived</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
